--- a/Dados/fechamento_mes.xlsx
+++ b/Dados/fechamento_mes.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capribr-my.sharepoint.com/personal/luizlopes_capribr_onmicrosoft_com/Documents/desempenho-ativos/Dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="11_CF0AF66F318CC9AA6A797A29F883C320F94EDBE9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{701F3489-CC62-4AF2-82A5-5D993C9B20C8}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="11_CF0AF66F318CC9AA6A797A29F883C320F94EDBE9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{158941BC-D48F-4E7A-8AAC-87FEB724FB01}"/>
   <bookViews>
-    <workbookView xWindow="5355" yWindow="1050" windowWidth="20490" windowHeight="15150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fechamento" sheetId="1" r:id="rId1"/>
     <sheet name="Glossário" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fechamento!$A$1:$D$21</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -879,6 +882,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D21" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D21">
+      <sortCondition descending="1" ref="C1:C21"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/Dados/fechamento_mes.xlsx
+++ b/Dados/fechamento_mes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capribr-my.sharepoint.com/personal/luizlopes_capribr_onmicrosoft_com/Documents/desempenho-ativos/Dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="11_CF0AF66F318CC9AA6A797A29F883C320F94EDBE9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{158941BC-D48F-4E7A-8AAC-87FEB724FB01}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="11_FF8C9E9FFEDC4CA6AC38F1E030E0454DF4EED53B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{884E970E-EBBA-458E-9C56-0B98955C9B16}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15180" yWindow="3615" windowWidth="11130" windowHeight="8505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fechamento" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fechamento!$A$1:$D$21</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="76">
   <si>
     <t>Dólar</t>
   </si>
@@ -140,9 +153,6 @@
     <t>Referência a um ETF ou índice de títulos de renda fixa de curto prazo de proteção à inflação.</t>
   </si>
   <si>
-    <t xml:space="preserve">% Acumulado No mes </t>
-  </si>
-  <si>
     <t>Índice de Debêntures próprio da JGP</t>
   </si>
   <si>
@@ -155,43 +165,67 @@
     <t>Dólar Index - Mede o valor do dólar americano contra uma cesta de moedas estrangeiras (a saber: EUR, JPY, GBP, CAD, SEK, CHF).</t>
   </si>
   <si>
+    <t>Valores representam o último dado disponível na fonte consultada</t>
+  </si>
+  <si>
+    <t>Fonte</t>
+  </si>
+  <si>
+    <t>Quantum Finance</t>
+  </si>
+  <si>
+    <t>Yahoo Finance</t>
+  </si>
+  <si>
+    <t>FRED</t>
+  </si>
+  <si>
     <t>Ativo</t>
   </si>
   <si>
     <t>Numero Indice</t>
   </si>
   <si>
-    <t>% Acumulado No mes Anualizado</t>
-  </si>
-  <si>
     <t>NDX</t>
   </si>
   <si>
     <t>SPX</t>
   </si>
   <si>
+    <t>DJI</t>
+  </si>
+  <si>
+    <t>Idex-Infra Geral JGP</t>
+  </si>
+  <si>
+    <t>IDA-IPCA Infraestrutura</t>
+  </si>
+  <si>
     <t>Idex-CDI Geral JGP</t>
   </si>
   <si>
+    <t>IDA-DI</t>
+  </si>
+  <si>
+    <t>RUT</t>
+  </si>
+  <si>
+    <t>DXY</t>
+  </si>
+  <si>
+    <t>CDI</t>
+  </si>
+  <si>
     <t>Dólar</t>
   </si>
   <si>
-    <t>IDA-DI</t>
-  </si>
-  <si>
-    <t>DJI</t>
-  </si>
-  <si>
-    <t>DXY</t>
-  </si>
-  <si>
-    <t>CDI</t>
+    <t>IMA-B 5</t>
   </si>
   <si>
     <t>IRF-M</t>
   </si>
   <si>
-    <t>IMA-B 5</t>
+    <t>SGOV</t>
   </si>
   <si>
     <t>HY</t>
@@ -200,43 +234,37 @@
     <t>STIP</t>
   </si>
   <si>
+    <t>IHFA</t>
+  </si>
+  <si>
+    <t>IMA-B</t>
+  </si>
+  <si>
     <t>TIP</t>
   </si>
   <si>
-    <t>SGOV</t>
+    <t>HG</t>
   </si>
   <si>
     <t>AGG</t>
   </si>
   <si>
-    <t>IHFA</t>
-  </si>
-  <si>
-    <t>HG</t>
-  </si>
-  <si>
-    <t>IMA-B</t>
-  </si>
-  <si>
-    <t>RUT</t>
-  </si>
-  <si>
     <t>Ibovespa</t>
   </si>
   <si>
-    <t>Valores representam o último dado disponível na fonte consultada</t>
-  </si>
-  <si>
-    <t>Fonte</t>
-  </si>
-  <si>
-    <t>Quantum Finance</t>
-  </si>
-  <si>
-    <t>Yahoo Finance</t>
-  </si>
-  <si>
-    <t>FRED</t>
+    <t>Var% no mes</t>
+  </si>
+  <si>
+    <t>Var% no mes anualizado</t>
+  </si>
+  <si>
+    <t>Selic</t>
+  </si>
+  <si>
+    <t>FFR</t>
+  </si>
+  <si>
+    <t>5,25-5,50</t>
   </si>
 </sst>
 </file>
@@ -272,8 +300,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -578,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" customWidth="1"/>
@@ -587,270 +616,274 @@
     <col min="4" max="4" width="31.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="D1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B2">
-        <v>17137.240234375</v>
+        <v>2054.84008789062</v>
       </c>
       <c r="C2">
-        <v>3.59</v>
+        <v>5.52</v>
       </c>
       <c r="D2">
-        <v>52.691195991206101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>90.553701987975003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B3">
-        <v>4845.64990234375</v>
+        <v>18043.849609375</v>
       </c>
       <c r="C3">
-        <v>2.17</v>
+        <v>5.29</v>
       </c>
       <c r="D3">
-        <v>29.384043803414201</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>85.628864566740305</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B4">
-        <v>1.7311919200000001</v>
+        <v>5096.27001953125</v>
       </c>
       <c r="C4">
-        <v>1.37</v>
+        <v>5.17</v>
       </c>
       <c r="D4">
-        <v>17.7371063704942</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>83.105962718151204</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B5">
-        <v>4.9535</v>
+        <v>1.3249498200000001</v>
       </c>
       <c r="C5">
-        <v>1.27</v>
+        <v>2.56</v>
       </c>
       <c r="D5">
-        <v>16.350892700314201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35.436632241544302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B6">
-        <v>3463.3843040000002</v>
+        <v>2165.0221329999999</v>
       </c>
       <c r="C6">
-        <v>1.25</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="D6">
-        <v>16.0754517722998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33.703739138840298</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
       <c r="B7">
-        <v>38150.30078125</v>
+        <v>38996.390625</v>
       </c>
       <c r="C7">
-        <v>1.1499999999999999</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="D7">
-        <v>14.7071911538915</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>30.145908509091601</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B8">
-        <v>103.26999664306599</v>
+        <v>3506.9396889999998</v>
       </c>
       <c r="C8">
-        <v>1.05</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D8">
-        <v>13.3537296586903</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14.8433488405669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9">
-        <v>3119.28927903162</v>
+        <v>1.75028067</v>
       </c>
       <c r="C9">
-        <v>0.92</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D9">
-        <v>11.616115026912601</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14.0286196499853</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="B10">
-        <v>18062.640669</v>
+        <v>129020.02</v>
       </c>
       <c r="C10">
-        <v>0.68</v>
+        <v>0.99</v>
       </c>
       <c r="D10">
-        <v>8.4722085025153095</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12.548695692601701</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B11">
-        <v>9037.6734560000004</v>
+        <v>104.16000366210901</v>
       </c>
       <c r="C11">
-        <v>0.64</v>
+        <v>0.86</v>
       </c>
       <c r="D11">
-        <v>7.9561870720073404</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10.8224037644802</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B12">
-        <v>1591.71</v>
+        <v>3144.30608223642</v>
       </c>
       <c r="C12">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="D12">
-        <v>7.5706487926186803</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10.0338693716146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B13">
-        <v>99.019996643066406</v>
+        <v>4.9832999999999998</v>
       </c>
       <c r="C13">
-        <v>0.51</v>
+        <v>0.6</v>
       </c>
       <c r="D13">
-        <v>6.2946180846381203</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7.4424167721924803</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B14">
-        <v>107.84999847412099</v>
+        <v>9091.293259</v>
       </c>
       <c r="C14">
-        <v>0.48</v>
+        <v>0.59</v>
       </c>
       <c r="D14">
-        <v>5.9145235035986001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7.3143248890742898</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B15">
-        <v>100.709999084473</v>
+        <v>9916.7625509999998</v>
       </c>
       <c r="C15">
-        <v>0.42</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="D15">
-        <v>5.15806944291164</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6.8033559467648397</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B16">
-        <v>99.099998474121094</v>
+        <v>18145.793172000002</v>
       </c>
       <c r="C16">
-        <v>0.32</v>
+        <v>0.46</v>
       </c>
       <c r="D16">
-        <v>3.9083101131259101</v>
+        <v>5.6618197194086903</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B17">
-        <v>5002.45</v>
+        <v>100.699996948242</v>
       </c>
       <c r="C17">
-        <v>0.11</v>
+        <v>0.45</v>
       </c>
       <c r="D17">
-        <v>1.32801535460079</v>
+        <v>5.5356751950101897</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B18">
-        <v>3229.13</v>
+        <v>1595.32</v>
       </c>
       <c r="C18">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D18">
-        <v>1.20662204957915</v>
+        <v>3.6599980288130101</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B19">
-        <v>9862.5606779999998</v>
+        <v>5006.45</v>
       </c>
       <c r="C19">
-        <v>-0.5</v>
+        <v>0.06</v>
       </c>
       <c r="D19">
-        <v>-5.8377193085624297</v>
+        <v>0.72238075842128202</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -858,27 +891,71 @@
         <v>64</v>
       </c>
       <c r="B20">
-        <v>1947.33996582031</v>
+        <v>98.870002746582003</v>
       </c>
       <c r="C20">
-        <v>-3.25</v>
+        <v>-0.15</v>
       </c>
       <c r="D20">
-        <v>-32.731509184701601</v>
+        <v>-1.78522400000656</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B21">
-        <v>127752.28</v>
+        <v>106.720001220703</v>
       </c>
       <c r="C21">
-        <v>-3.73</v>
+        <v>-1.05</v>
       </c>
       <c r="D21">
-        <v>-36.628839287082101</v>
+        <v>-11.8972260598385</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22">
+        <v>3198.37</v>
+      </c>
+      <c r="C22">
+        <v>-1.4</v>
+      </c>
+      <c r="D22">
+        <v>-15.5649083162078</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23">
+        <v>97.349998474121094</v>
+      </c>
+      <c r="C23">
+        <v>-1.47</v>
+      </c>
+      <c r="D23">
+        <v>-16.281431552392299</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24">
+        <v>11.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -899,7 +976,7 @@
   <cols>
     <col min="1" max="1" width="17.5703125" customWidth="1"/>
     <col min="2" max="2" width="117" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -910,7 +987,7 @@
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -921,7 +998,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -932,7 +1009,7 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -943,7 +1020,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -951,10 +1028,10 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,10 +1039,10 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -973,10 +1050,10 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -984,10 +1061,10 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -998,7 +1075,7 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1009,7 +1086,7 @@
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1020,7 +1097,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1031,7 +1108,7 @@
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1042,7 +1119,7 @@
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1053,7 +1130,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1064,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1075,7 +1152,7 @@
         <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1086,7 +1163,7 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1097,7 +1174,7 @@
         <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1108,7 +1185,7 @@
         <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1119,7 +1196,7 @@
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1130,12 +1207,12 @@
         <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/Dados/fechamento_mes.xlsx
+++ b/Dados/fechamento_mes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capribr-my.sharepoint.com/personal/luizlopes_capribr_onmicrosoft_com/Documents/desempenho-ativos/Dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="11_FF8C9E9FFEDC4CA6AC38F1E030E0454DF4EED53B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{884E970E-EBBA-458E-9C56-0B98955C9B16}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_FD14D649DF42CB4AE7D146D91486FC5828747A52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3DCB901-2D19-4195-90E9-3E7DC0A7649A}"/>
   <bookViews>
-    <workbookView xWindow="-15180" yWindow="3615" windowWidth="11130" windowHeight="8505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fechamento" sheetId="1" r:id="rId1"/>
@@ -19,25 +19,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fechamento!$A$1:$D$21</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="79">
   <si>
     <t>Dólar</t>
   </si>
@@ -180,18 +167,33 @@
     <t>FRED</t>
   </si>
   <si>
+    <t>Selic</t>
+  </si>
+  <si>
+    <t>FFR</t>
+  </si>
+  <si>
+    <t>5,25-5,50</t>
+  </si>
+  <si>
     <t>Ativo</t>
   </si>
   <si>
-    <t>Numero Indice</t>
-  </si>
-  <si>
-    <t>NDX</t>
+    <t>Var% no mes</t>
+  </si>
+  <si>
+    <t>Var% no mes anualizado</t>
+  </si>
+  <si>
+    <t>RUT</t>
   </si>
   <si>
     <t>SPX</t>
   </si>
   <si>
+    <t>IXIC</t>
+  </si>
+  <si>
     <t>DJI</t>
   </si>
   <si>
@@ -207,77 +209,79 @@
     <t>IDA-DI</t>
   </si>
   <si>
-    <t>RUT</t>
+    <t>CDI</t>
+  </si>
+  <si>
+    <t>HY</t>
   </si>
   <si>
     <t>DXY</t>
   </si>
   <si>
-    <t>CDI</t>
+    <t>IMA-B 5</t>
+  </si>
+  <si>
+    <t>IRF-M</t>
   </si>
   <si>
     <t>Dólar</t>
   </si>
   <si>
-    <t>IMA-B 5</t>
-  </si>
-  <si>
-    <t>IRF-M</t>
-  </si>
-  <si>
     <t>SGOV</t>
   </si>
   <si>
-    <t>HY</t>
+    <t>IHFA</t>
   </si>
   <si>
     <t>STIP</t>
   </si>
   <si>
-    <t>IHFA</t>
-  </si>
-  <si>
     <t>IMA-B</t>
   </si>
   <si>
+    <t>HG</t>
+  </si>
+  <si>
     <t>TIP</t>
   </si>
   <si>
-    <t>HG</t>
+    <t>Ibovespa</t>
   </si>
   <si>
     <t>AGG</t>
   </si>
   <si>
-    <t>Ibovespa</t>
-  </si>
-  <si>
-    <t>Var% no mes</t>
-  </si>
-  <si>
-    <t>Var% no mes anualizado</t>
-  </si>
-  <si>
-    <t>Selic</t>
-  </si>
-  <si>
-    <t>FFR</t>
-  </si>
-  <si>
-    <t>5,25-5,50</t>
+    <t>Var% em 12 meses</t>
+  </si>
+  <si>
+    <t>Var% no ano</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Número índice</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -300,9 +304,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -607,355 +612,700 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" customWidth="1"/>
     <col min="2" max="2" width="19.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>45379</v>
+      </c>
+      <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2">
+        <v>2124.55004882812</v>
+      </c>
+      <c r="D2">
+        <v>3.39</v>
+      </c>
+      <c r="E2">
+        <v>49.190930936488598</v>
+      </c>
+      <c r="F2">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="G2">
+        <v>21.2206822266619</v>
+      </c>
+      <c r="H2">
+        <v>49.190930936488598</v>
+      </c>
+      <c r="I2">
+        <v>4.8099999999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>45379</v>
+      </c>
+      <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3">
+        <v>5254.35009765625</v>
+      </c>
+      <c r="D3">
+        <v>3.1</v>
+      </c>
+      <c r="E3">
+        <v>44.246067945403396</v>
+      </c>
+      <c r="F3" s="1">
+        <v>10.16</v>
+      </c>
+      <c r="G3">
+        <v>32.309061630527097</v>
+      </c>
+      <c r="H3" s="1">
+        <v>44.246067945403396</v>
+      </c>
+      <c r="I3">
+        <v>10.16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>45379</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4">
+        <v>39807.37109375</v>
+      </c>
+      <c r="D4">
+        <v>2.08</v>
+      </c>
+      <c r="E4">
+        <v>28.022981310051499</v>
+      </c>
+      <c r="F4" s="1">
+        <v>5.62</v>
+      </c>
+      <c r="G4" s="1">
+        <v>22.884064590938198</v>
+      </c>
+      <c r="H4">
+        <v>28.022981310051499</v>
+      </c>
+      <c r="I4">
+        <v>5.62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>45379</v>
+      </c>
+      <c r="B5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5">
+        <v>16379.4599609375</v>
+      </c>
+      <c r="D5">
+        <v>1.79</v>
+      </c>
+      <c r="E5">
+        <v>23.726113884365802</v>
+      </c>
+      <c r="F5">
+        <v>9.11</v>
+      </c>
+      <c r="G5">
+        <v>39.803243505645398</v>
+      </c>
+      <c r="H5">
+        <v>23.726113884365802</v>
+      </c>
+      <c r="I5">
+        <v>9.11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>45378</v>
+      </c>
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6">
+        <v>1.77220493</v>
+      </c>
+      <c r="D6">
+        <v>1.19</v>
+      </c>
+      <c r="E6">
+        <v>15.2527113059203</v>
+      </c>
+      <c r="F6">
+        <v>3.96</v>
+      </c>
+      <c r="G6">
+        <v>17.990818752604799</v>
+      </c>
+      <c r="H6">
+        <v>15.2527113059203</v>
+      </c>
+      <c r="I6">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>45379</v>
+      </c>
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7">
+        <v>3235.5</v>
+      </c>
+      <c r="D7">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="E7">
+        <v>14.8433488405669</v>
+      </c>
+      <c r="F7">
+        <v>-0.1</v>
+      </c>
+      <c r="G7">
+        <v>3.9304367937196001</v>
+      </c>
+      <c r="H7">
+        <v>14.8433488405669</v>
+      </c>
+      <c r="I7">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>45379</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8">
+        <v>1613.75</v>
+      </c>
+      <c r="D8">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="E8">
+        <v>14.8433488405669</v>
+      </c>
+      <c r="F8">
+        <v>1.47</v>
+      </c>
+      <c r="G8">
+        <v>10.449119829167399</v>
+      </c>
+      <c r="H8">
+        <v>14.8433488405669</v>
+      </c>
+      <c r="I8">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>45378</v>
+      </c>
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9">
+        <v>3547.3531370000001</v>
+      </c>
+      <c r="D9">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E9">
+        <v>14.7071911538915</v>
+      </c>
+      <c r="F9">
+        <v>3.75</v>
+      </c>
+      <c r="G9">
+        <v>17.065620366525799</v>
+      </c>
+      <c r="H9">
+        <v>14.7071911538915</v>
+      </c>
+      <c r="I9">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>45379</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10">
+        <v>3170.5132617365298</v>
+      </c>
+      <c r="D10">
+        <v>0.83</v>
+      </c>
+      <c r="E10">
+        <v>10.4274913828344</v>
+      </c>
+      <c r="F10">
+        <v>2.62</v>
+      </c>
+      <c r="G10">
+        <v>12.647874654397601</v>
+      </c>
+      <c r="H10">
+        <v>10.4274913828344</v>
+      </c>
+      <c r="I10">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>45379</v>
+      </c>
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11">
+        <v>9161.3082840000006</v>
+      </c>
+      <c r="D11">
+        <v>0.77</v>
+      </c>
+      <c r="E11">
+        <v>9.6415338967120103</v>
+      </c>
+      <c r="F11">
+        <v>2.06</v>
+      </c>
+      <c r="G11">
+        <v>9.6603737303409201</v>
+      </c>
+      <c r="H11">
+        <v>9.6415338967120103</v>
+      </c>
+      <c r="I11">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>45376</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12">
+        <v>5043.84</v>
+      </c>
+      <c r="D12">
+        <v>0.66</v>
+      </c>
+      <c r="E12">
+        <v>8.2139158364711307</v>
+      </c>
+      <c r="F12">
+        <v>0.48</v>
+      </c>
+      <c r="G12">
+        <v>9.4155928673693694</v>
+      </c>
+      <c r="H12">
+        <v>8.2139158364711307</v>
+      </c>
+      <c r="I12">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>45379</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13">
+        <v>107.41000366210901</v>
+      </c>
+      <c r="D13">
+        <v>0.65</v>
+      </c>
+      <c r="E13">
+        <v>8.0849810365515502</v>
+      </c>
+      <c r="F13">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="G13">
+        <v>0.939536915940686</v>
+      </c>
+      <c r="H13">
+        <v>8.0849810365515502</v>
+      </c>
+      <c r="I13">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>45379</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14">
+        <v>97.940002441406193</v>
+      </c>
+      <c r="D14">
+        <v>0.61</v>
+      </c>
+      <c r="E14">
+        <v>7.5706487926186803</v>
+      </c>
+      <c r="F14">
+        <v>-1.03</v>
+      </c>
+      <c r="G14">
+        <v>2.0227736984025402</v>
+      </c>
+      <c r="H14">
+        <v>7.5706487926186803</v>
+      </c>
+      <c r="I14">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>45379</v>
+      </c>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15">
+        <v>99.430000305175795</v>
+      </c>
+      <c r="D15">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E15">
+        <v>7.0585609779296297</v>
+      </c>
+      <c r="F15">
+        <v>0.85</v>
+      </c>
+      <c r="G15">
+        <v>3.51782172107167</v>
+      </c>
+      <c r="H15">
+        <v>7.0585609779296297</v>
+      </c>
+      <c r="I15">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>45379</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16">
+        <v>18243.935332000001</v>
+      </c>
+      <c r="D16">
+        <v>0.54</v>
+      </c>
+      <c r="E16">
+        <v>6.6759626640876801</v>
+      </c>
+      <c r="F16">
+        <v>1.68</v>
+      </c>
+      <c r="G16">
+        <v>14.4531020083786</v>
+      </c>
+      <c r="H16">
+        <v>6.6759626640876801</v>
+      </c>
+      <c r="I16">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>45378</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17">
+        <v>2176.540516</v>
+      </c>
+      <c r="D17">
+        <v>0.53</v>
+      </c>
+      <c r="E17">
+        <v>6.5487086851492098</v>
+      </c>
+      <c r="F17">
+        <v>3.68</v>
+      </c>
+      <c r="G17">
+        <v>19.147293871192002</v>
+      </c>
+      <c r="H17">
+        <v>6.5487086851492098</v>
+      </c>
+      <c r="I17">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>45378</v>
+      </c>
+      <c r="B18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18">
+        <v>1.33319297</v>
+      </c>
+      <c r="D18">
+        <v>0.48</v>
+      </c>
+      <c r="E18">
+        <v>5.9145235035986001</v>
+      </c>
+      <c r="F18">
+        <v>3.85</v>
+      </c>
+      <c r="G18">
+        <v>19.430945808764701</v>
+      </c>
+      <c r="H18">
+        <v>5.9145235035986001</v>
+      </c>
+      <c r="I18">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>45379</v>
+      </c>
+      <c r="B19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19">
+        <v>104.550003051758</v>
+      </c>
+      <c r="D19">
+        <v>0.37</v>
+      </c>
+      <c r="E19">
+        <v>4.53147769825524</v>
+      </c>
+      <c r="F19">
+        <v>3.18</v>
+      </c>
+      <c r="G19">
+        <v>2.0697088160359902</v>
+      </c>
+      <c r="H19">
+        <v>4.53147769825524</v>
+      </c>
+      <c r="I19">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>45379</v>
+      </c>
+      <c r="B20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20">
+        <v>4.9962</v>
+      </c>
+      <c r="D20">
+        <v>0.26</v>
+      </c>
+      <c r="E20">
+        <v>3.1650049434697798</v>
+      </c>
+      <c r="F20">
+        <v>3.2</v>
+      </c>
+      <c r="G20">
+        <v>-5.5913531490334796</v>
+      </c>
+      <c r="H20">
+        <v>3.1650049434697798</v>
+      </c>
+      <c r="I20">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>45379</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21">
+        <v>9924.4778029999998</v>
+      </c>
+      <c r="D21">
+        <v>0.08</v>
+      </c>
+      <c r="E21">
+        <v>0.96423528430107397</v>
+      </c>
+      <c r="F21">
+        <v>0.18</v>
+      </c>
+      <c r="G21">
+        <v>12.1124706484204</v>
+      </c>
+      <c r="H21">
+        <v>0.96423528430107397</v>
+      </c>
+      <c r="I21">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>45379</v>
+      </c>
+      <c r="B22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22">
+        <v>100.709999084473</v>
+      </c>
+      <c r="D22">
+        <v>0.01</v>
+      </c>
+      <c r="E22">
+        <v>0.120066022004939</v>
+      </c>
+      <c r="F22">
+        <v>0.9</v>
+      </c>
+      <c r="G22">
+        <v>4.9386824398049098</v>
+      </c>
+      <c r="H22">
+        <v>0.120066022004939</v>
+      </c>
+      <c r="I22">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>45379</v>
+      </c>
+      <c r="B23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23">
+        <v>128106.1</v>
+      </c>
+      <c r="D23">
+        <v>-0.71</v>
+      </c>
+      <c r="E23">
+        <v>-8.1950436713639405</v>
+      </c>
+      <c r="F23">
+        <v>-4.53</v>
+      </c>
+      <c r="G23">
+        <v>29.6236428742214</v>
+      </c>
+      <c r="H23">
+        <v>-8.1950436713639405</v>
+      </c>
+      <c r="I23">
+        <v>-4.53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
         <v>47</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C24">
+        <v>10.75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
         <v>48</v>
       </c>
-      <c r="C1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2">
-        <v>2054.84008789062</v>
-      </c>
-      <c r="C2">
-        <v>5.52</v>
-      </c>
-      <c r="D2">
-        <v>90.553701987975003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C25" t="s">
         <v>49</v>
-      </c>
-      <c r="B3">
-        <v>18043.849609375</v>
-      </c>
-      <c r="C3">
-        <v>5.29</v>
-      </c>
-      <c r="D3">
-        <v>85.628864566740305</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4">
-        <v>5096.27001953125</v>
-      </c>
-      <c r="C4">
-        <v>5.17</v>
-      </c>
-      <c r="D4">
-        <v>83.105962718151204</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5">
-        <v>1.3249498200000001</v>
-      </c>
-      <c r="C5">
-        <v>2.56</v>
-      </c>
-      <c r="D5">
-        <v>35.436632241544302</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6">
-        <v>2165.0221329999999</v>
-      </c>
-      <c r="C6">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="D6">
-        <v>33.703739138840298</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7">
-        <v>38996.390625</v>
-      </c>
-      <c r="C7">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="D7">
-        <v>30.145908509091601</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8">
-        <v>3506.9396889999998</v>
-      </c>
-      <c r="C8">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="D8">
-        <v>14.8433488405669</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9">
-        <v>1.75028067</v>
-      </c>
-      <c r="C9">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D9">
-        <v>14.0286196499853</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10">
-        <v>129020.02</v>
-      </c>
-      <c r="C10">
-        <v>0.99</v>
-      </c>
-      <c r="D10">
-        <v>12.548695692601701</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11">
-        <v>104.16000366210901</v>
-      </c>
-      <c r="C11">
-        <v>0.86</v>
-      </c>
-      <c r="D11">
-        <v>10.8224037644802</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12">
-        <v>3144.30608223642</v>
-      </c>
-      <c r="C12">
-        <v>0.8</v>
-      </c>
-      <c r="D12">
-        <v>10.0338693716146</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13">
-        <v>4.9832999999999998</v>
-      </c>
-      <c r="C13">
-        <v>0.6</v>
-      </c>
-      <c r="D13">
-        <v>7.4424167721924803</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14">
-        <v>9091.293259</v>
-      </c>
-      <c r="C14">
-        <v>0.59</v>
-      </c>
-      <c r="D14">
-        <v>7.3143248890742898</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15">
-        <v>9916.7625509999998</v>
-      </c>
-      <c r="C15">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="D15">
-        <v>6.8033559467648397</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16">
-        <v>18145.793172000002</v>
-      </c>
-      <c r="C16">
-        <v>0.46</v>
-      </c>
-      <c r="D16">
-        <v>5.6618197194086903</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>62</v>
-      </c>
-      <c r="B17">
-        <v>100.699996948242</v>
-      </c>
-      <c r="C17">
-        <v>0.45</v>
-      </c>
-      <c r="D17">
-        <v>5.5356751950101897</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18">
-        <v>1595.32</v>
-      </c>
-      <c r="C18">
-        <v>0.3</v>
-      </c>
-      <c r="D18">
-        <v>3.6599980288130101</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>65</v>
-      </c>
-      <c r="B19">
-        <v>5006.45</v>
-      </c>
-      <c r="C19">
-        <v>0.06</v>
-      </c>
-      <c r="D19">
-        <v>0.72238075842128202</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20">
-        <v>98.870002746582003</v>
-      </c>
-      <c r="C20">
-        <v>-0.15</v>
-      </c>
-      <c r="D20">
-        <v>-1.78522400000656</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>67</v>
-      </c>
-      <c r="B21">
-        <v>106.720001220703</v>
-      </c>
-      <c r="C21">
-        <v>-1.05</v>
-      </c>
-      <c r="D21">
-        <v>-11.8972260598385</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22">
-        <v>3198.37</v>
-      </c>
-      <c r="C22">
-        <v>-1.4</v>
-      </c>
-      <c r="D22">
-        <v>-15.5649083162078</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>69</v>
-      </c>
-      <c r="B23">
-        <v>97.349998474121094</v>
-      </c>
-      <c r="C23">
-        <v>-1.47</v>
-      </c>
-      <c r="D23">
-        <v>-16.281431552392299</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24">
-        <v>11.25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/Dados/fechamento_mes.xlsx
+++ b/Dados/fechamento_mes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capribr-my.sharepoint.com/personal/luizlopes_capribr_onmicrosoft_com/Documents/desempenho-ativos/Dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_FD14D649DF42CB4AE7D146D91486FC5828747A52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3DCB901-2D19-4195-90E9-3E7DC0A7649A}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_FD14D649DF42729A60CED491CC6763CAFC6977FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FB5B5A1-837E-4A4F-877C-B3BECC9F1D75}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6120" yWindow="1455" windowWidth="19725" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fechamento" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="80">
   <si>
     <t>Dólar</t>
   </si>
@@ -170,10 +170,16 @@
     <t>Selic</t>
   </si>
   <si>
-    <t>FFR</t>
-  </si>
-  <si>
-    <t>5,25-5,50</t>
+    <t>Var% no mes anualizado</t>
+  </si>
+  <si>
+    <t>Var% no ano</t>
+  </si>
+  <si>
+    <t>Número Índice</t>
+  </si>
+  <si>
+    <t>Data</t>
   </si>
   <si>
     <t>Ativo</t>
@@ -185,82 +191,79 @@
     <t>Var% no mes anualizado</t>
   </si>
   <si>
+    <t>Var% no ano</t>
+  </si>
+  <si>
+    <t>Var% em 12 meses</t>
+  </si>
+  <si>
+    <t>Dólar</t>
+  </si>
+  <si>
+    <t>DXY</t>
+  </si>
+  <si>
+    <t>IDA-DI</t>
+  </si>
+  <si>
+    <t>Idex-CDI Geral JGP</t>
+  </si>
+  <si>
+    <t>CDI</t>
+  </si>
+  <si>
+    <t>SGOV</t>
+  </si>
+  <si>
+    <t>STIP</t>
+  </si>
+  <si>
+    <t>IMA-B 5</t>
+  </si>
+  <si>
+    <t>IRF-M</t>
+  </si>
+  <si>
+    <t>HY</t>
+  </si>
+  <si>
+    <t>IHFA</t>
+  </si>
+  <si>
+    <t>Idex-Infra Geral JGP</t>
+  </si>
+  <si>
+    <t>IMA-B</t>
+  </si>
+  <si>
+    <t>IDA-IPCA Infraestrutura</t>
+  </si>
+  <si>
+    <t>TIP</t>
+  </si>
+  <si>
+    <t>Ibovespa</t>
+  </si>
+  <si>
+    <t>HG</t>
+  </si>
+  <si>
+    <t>AGG</t>
+  </si>
+  <si>
+    <t>SPX</t>
+  </si>
+  <si>
+    <t>IXIC</t>
+  </si>
+  <si>
+    <t>DJI</t>
+  </si>
+  <si>
     <t>RUT</t>
   </si>
   <si>
-    <t>SPX</t>
-  </si>
-  <si>
-    <t>IXIC</t>
-  </si>
-  <si>
-    <t>DJI</t>
-  </si>
-  <si>
-    <t>Idex-Infra Geral JGP</t>
-  </si>
-  <si>
-    <t>IDA-IPCA Infraestrutura</t>
-  </si>
-  <si>
-    <t>Idex-CDI Geral JGP</t>
-  </si>
-  <si>
-    <t>IDA-DI</t>
-  </si>
-  <si>
-    <t>CDI</t>
-  </si>
-  <si>
-    <t>HY</t>
-  </si>
-  <si>
-    <t>DXY</t>
-  </si>
-  <si>
-    <t>IMA-B 5</t>
-  </si>
-  <si>
-    <t>IRF-M</t>
-  </si>
-  <si>
-    <t>Dólar</t>
-  </si>
-  <si>
-    <t>SGOV</t>
-  </si>
-  <si>
-    <t>IHFA</t>
-  </si>
-  <si>
-    <t>STIP</t>
-  </si>
-  <si>
-    <t>IMA-B</t>
-  </si>
-  <si>
-    <t>HG</t>
-  </si>
-  <si>
-    <t>TIP</t>
-  </si>
-  <si>
-    <t>Ibovespa</t>
-  </si>
-  <si>
-    <t>AGG</t>
-  </si>
-  <si>
-    <t>Var% em 12 meses</t>
-  </si>
-  <si>
-    <t>Var% no ano</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Número índice</t>
+    <t>FFR (upper bound)</t>
   </si>
 </sst>
 </file>
@@ -304,10 +307,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -615,66 +619,67 @@
   <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" customWidth="1"/>
+    <col min="8" max="8" width="22.85546875" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="B1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C1" t="s">
-        <v>78</v>
-      </c>
       <c r="D1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F1" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="G1" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="H1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I1" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>45379</v>
+        <v>45412</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2">
-        <v>2124.55004882812</v>
+        <v>57</v>
+      </c>
+      <c r="C2" s="3">
+        <v>5.1718000000000002</v>
       </c>
       <c r="D2">
-        <v>3.39</v>
+        <v>3.51</v>
       </c>
       <c r="E2">
-        <v>49.190930936488598</v>
+        <v>51.282155230213597</v>
       </c>
       <c r="F2">
-        <v>4.8099999999999996</v>
+        <v>6.83</v>
       </c>
       <c r="G2">
-        <v>21.2206822266619</v>
+        <v>3.1266201395813198</v>
       </c>
       <c r="H2">
         <v>49.190930936488598</v>
@@ -685,25 +690,25 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>45379</v>
+        <v>45412</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3">
-        <v>5254.35009765625</v>
+        <v>58</v>
+      </c>
+      <c r="C3" s="3">
+        <v>106.220001220703</v>
       </c>
       <c r="D3">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="E3">
-        <v>44.246067945403396</v>
+        <v>20.983040650908201</v>
       </c>
       <c r="F3" s="1">
-        <v>10.16</v>
+        <v>4.83</v>
       </c>
       <c r="G3">
-        <v>32.309061630527097</v>
+        <v>4.4752661883566498</v>
       </c>
       <c r="H3" s="1">
         <v>44.246067945403396</v>
@@ -714,25 +719,25 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>45379</v>
+        <v>45412</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4">
-        <v>39807.37109375</v>
+        <v>59</v>
+      </c>
+      <c r="C4" s="3">
+        <v>3583.856029</v>
       </c>
       <c r="D4">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="E4">
-        <v>28.022981310051499</v>
+        <v>12.816456143923499</v>
       </c>
       <c r="F4" s="1">
-        <v>5.62</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="G4" s="1">
-        <v>22.884064590938198</v>
+        <v>16.9853047203942</v>
       </c>
       <c r="H4">
         <v>28.022981310051499</v>
@@ -743,25 +748,25 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>45379</v>
+        <v>45411</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5">
-        <v>16379.4599609375</v>
+        <v>60</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1.78922946</v>
       </c>
       <c r="D5">
-        <v>1.79</v>
+        <v>0.94</v>
       </c>
       <c r="E5">
-        <v>23.726113884365802</v>
+        <v>11.881841195515699</v>
       </c>
       <c r="F5">
-        <v>9.11</v>
+        <v>4.95</v>
       </c>
       <c r="G5">
-        <v>39.803243505645398</v>
+        <v>17.590183061214301</v>
       </c>
       <c r="H5">
         <v>23.726113884365802</v>
@@ -772,25 +777,25 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>45378</v>
+        <v>45412</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6">
-        <v>1.77220493</v>
+        <v>61</v>
+      </c>
+      <c r="C6" s="3">
+        <v>3198.6491236259999</v>
       </c>
       <c r="D6">
-        <v>1.19</v>
+        <v>0.89</v>
       </c>
       <c r="E6">
-        <v>15.2527113059203</v>
+        <v>11.2186103609413</v>
       </c>
       <c r="F6">
-        <v>3.96</v>
+        <v>3.54</v>
       </c>
       <c r="G6">
-        <v>17.990818752604799</v>
+        <v>12.385098482992801</v>
       </c>
       <c r="H6">
         <v>15.2527113059203</v>
@@ -801,25 +806,25 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>45379</v>
+        <v>45412</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7">
-        <v>3235.5</v>
+        <v>62</v>
+      </c>
+      <c r="C7" s="3">
+        <v>100.27199554443401</v>
       </c>
       <c r="D7">
-        <v>1.1599999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="E7">
-        <v>14.8433488405669</v>
+        <v>5.40966873236182</v>
       </c>
       <c r="F7">
-        <v>-0.1</v>
+        <v>1.34</v>
       </c>
       <c r="G7">
-        <v>3.9304367937196001</v>
+        <v>4.9989929792960197</v>
       </c>
       <c r="H7">
         <v>14.8433488405669</v>
@@ -830,25 +835,25 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>45379</v>
+        <v>45412</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8">
-        <v>1613.75</v>
+        <v>63</v>
+      </c>
+      <c r="C8" s="3">
+        <v>98.568000793457003</v>
       </c>
       <c r="D8">
-        <v>1.1599999999999999</v>
+        <v>-0.17</v>
       </c>
       <c r="E8">
-        <v>14.8433488405669</v>
+        <v>-2.0210336736933998</v>
       </c>
       <c r="F8">
-        <v>1.47</v>
+        <v>0.68</v>
       </c>
       <c r="G8">
-        <v>10.449119829167399</v>
+        <v>2.8005878636553101</v>
       </c>
       <c r="H8">
         <v>14.8433488405669</v>
@@ -859,25 +864,25 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>45378</v>
+        <v>45412</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9">
-        <v>3547.3531370000001</v>
+        <v>64</v>
+      </c>
+      <c r="C9" s="3">
+        <v>9142.7225539999999</v>
       </c>
       <c r="D9">
-        <v>1.1499999999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="E9">
-        <v>14.7071911538915</v>
+        <v>-2.3737752105284899</v>
       </c>
       <c r="F9">
-        <v>3.75</v>
+        <v>1.85</v>
       </c>
       <c r="G9">
-        <v>17.065620366525799</v>
+        <v>8.3152877595076298</v>
       </c>
       <c r="H9">
         <v>14.7071911538915</v>
@@ -888,25 +893,25 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>45379</v>
+        <v>45412</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10">
-        <v>3170.5132617365298</v>
+        <v>65</v>
+      </c>
+      <c r="C10" s="3">
+        <v>18148.423220000001</v>
       </c>
       <c r="D10">
-        <v>0.83</v>
+        <v>-0.52</v>
       </c>
       <c r="E10">
-        <v>10.4274913828344</v>
+        <v>-6.06459348280368</v>
       </c>
       <c r="F10">
-        <v>2.62</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="G10">
-        <v>12.647874654397601</v>
+        <v>12.016316962550899</v>
       </c>
       <c r="H10">
         <v>10.4274913828344</v>
@@ -917,25 +922,25 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>45379</v>
+        <v>45412</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11">
-        <v>9161.3082840000006</v>
+        <v>66</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1598.18</v>
       </c>
       <c r="D11">
-        <v>0.77</v>
+        <v>-1</v>
       </c>
       <c r="E11">
-        <v>9.6415338967120103</v>
+        <v>-11.361512828387101</v>
       </c>
       <c r="F11">
-        <v>2.06</v>
+        <v>0.49</v>
       </c>
       <c r="G11">
-        <v>9.6603737303409201</v>
+        <v>9.3625116329993894</v>
       </c>
       <c r="H11">
         <v>9.6415338967120103</v>
@@ -946,25 +951,25 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>45376</v>
+        <v>45408</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12">
-        <v>5043.84</v>
+        <v>67</v>
+      </c>
+      <c r="C12" s="3">
+        <v>5000.43</v>
       </c>
       <c r="D12">
-        <v>0.66</v>
+        <v>-1.05</v>
       </c>
       <c r="E12">
-        <v>8.2139158364711307</v>
+        <v>-11.8972260598385</v>
       </c>
       <c r="F12">
-        <v>0.48</v>
+        <v>-0.38</v>
       </c>
       <c r="G12">
-        <v>9.4155928673693694</v>
+        <v>7.1662326807470098</v>
       </c>
       <c r="H12">
         <v>8.2139158364711307</v>
@@ -975,25 +980,25 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>45379</v>
+        <v>45411</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13">
-        <v>107.41000366210901</v>
+        <v>68</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1.3198431500000001</v>
       </c>
       <c r="D13">
-        <v>0.65</v>
+        <v>-1.19</v>
       </c>
       <c r="E13">
-        <v>8.0849810365515502</v>
+        <v>-13.3814734952748</v>
       </c>
       <c r="F13">
-        <v>-7.0000000000000007E-2</v>
+        <v>2.81</v>
       </c>
       <c r="G13">
-        <v>0.939536915940686</v>
+        <v>15.833515836683199</v>
       </c>
       <c r="H13">
         <v>8.0849810365515502</v>
@@ -1004,25 +1009,25 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>45379</v>
+        <v>45412</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14">
-        <v>97.940002441406193</v>
+        <v>69</v>
+      </c>
+      <c r="C14" s="3">
+        <v>9764.2466420000001</v>
       </c>
       <c r="D14">
-        <v>0.61</v>
+        <v>-1.61</v>
       </c>
       <c r="E14">
-        <v>7.5706487926186803</v>
+        <v>-17.697784373517798</v>
       </c>
       <c r="F14">
-        <v>-1.03</v>
+        <v>-1.44</v>
       </c>
       <c r="G14">
-        <v>2.0227736984025402</v>
+        <v>7.6248588742959997</v>
       </c>
       <c r="H14">
         <v>7.5706487926186803</v>
@@ -1033,25 +1038,25 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>45379</v>
+        <v>45412</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15">
-        <v>99.430000305175795</v>
+        <v>70</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2139.6358599999999</v>
       </c>
       <c r="D15">
-        <v>0.56999999999999995</v>
+        <v>-1.68</v>
       </c>
       <c r="E15">
-        <v>7.0585609779296297</v>
+        <v>-18.397692706630799</v>
       </c>
       <c r="F15">
-        <v>0.85</v>
+        <v>1.92</v>
       </c>
       <c r="G15">
-        <v>3.51782172107167</v>
+        <v>14.661723748123</v>
       </c>
       <c r="H15">
         <v>7.0585609779296297</v>
@@ -1062,25 +1067,25 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>45379</v>
+        <v>45412</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16">
-        <v>18243.935332000001</v>
+        <v>71</v>
+      </c>
+      <c r="C16" s="3">
+        <v>105.529998779297</v>
       </c>
       <c r="D16">
-        <v>0.54</v>
+        <v>-1.69</v>
       </c>
       <c r="E16">
-        <v>6.6759626640876801</v>
+        <v>-18.497232992970702</v>
       </c>
       <c r="F16">
-        <v>1.68</v>
+        <v>-1.76</v>
       </c>
       <c r="G16">
-        <v>14.4531020083786</v>
+        <v>-1.60115483246061</v>
       </c>
       <c r="H16">
         <v>6.6759626640876801</v>
@@ -1091,25 +1096,25 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>45378</v>
+        <v>45412</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17">
-        <v>2176.540516</v>
+        <v>72</v>
+      </c>
+      <c r="C17" s="3">
+        <v>125924.19</v>
       </c>
       <c r="D17">
-        <v>0.53</v>
+        <v>-1.7</v>
       </c>
       <c r="E17">
-        <v>6.5487086851492098</v>
+        <v>-18.596661965019202</v>
       </c>
       <c r="F17">
-        <v>3.68</v>
+        <v>-6.16</v>
       </c>
       <c r="G17">
-        <v>19.147293871192002</v>
+        <v>22.347590647832899</v>
       </c>
       <c r="H17">
         <v>6.5487086851492098</v>
@@ -1120,25 +1125,25 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>45378</v>
+        <v>45412</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18">
-        <v>1.33319297</v>
+        <v>73</v>
+      </c>
+      <c r="C18" s="3">
+        <v>3160.95</v>
       </c>
       <c r="D18">
-        <v>0.48</v>
+        <v>-2.33</v>
       </c>
       <c r="E18">
-        <v>5.9145235035986001</v>
+        <v>-24.641151689780699</v>
       </c>
       <c r="F18">
-        <v>3.85</v>
+        <v>-2.41</v>
       </c>
       <c r="G18">
-        <v>19.430945808764701</v>
+        <v>2.06028787849448</v>
       </c>
       <c r="H18">
         <v>5.9145235035986001</v>
@@ -1149,25 +1154,25 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>45379</v>
+        <v>45412</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19">
-        <v>104.550003051758</v>
+        <v>74</v>
+      </c>
+      <c r="C19" s="3">
+        <v>94.935005187988295</v>
       </c>
       <c r="D19">
-        <v>0.37</v>
+        <v>-2.48</v>
       </c>
       <c r="E19">
-        <v>4.53147769825524</v>
+        <v>-26.018299194832501</v>
       </c>
       <c r="F19">
-        <v>3.18</v>
+        <v>-3.48</v>
       </c>
       <c r="G19">
-        <v>2.0697088160359902</v>
+        <v>-1.77983637762208</v>
       </c>
       <c r="H19">
         <v>4.53147769825524</v>
@@ -1178,25 +1183,25 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>45379</v>
+        <v>45412</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20">
-        <v>4.9962</v>
+        <v>75</v>
+      </c>
+      <c r="C20" s="3">
+        <v>5035.68994140625</v>
       </c>
       <c r="D20">
-        <v>0.26</v>
+        <v>-4.16</v>
       </c>
       <c r="E20">
-        <v>3.1650049434697798</v>
+        <v>-39.943272941690303</v>
       </c>
       <c r="F20">
-        <v>3.2</v>
+        <v>5.57</v>
       </c>
       <c r="G20">
-        <v>-5.5913531490334796</v>
+        <v>20.775011871866798</v>
       </c>
       <c r="H20">
         <v>3.1650049434697798</v>
@@ -1207,25 +1212,25 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>45379</v>
+        <v>45412</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21">
-        <v>9924.4778029999998</v>
+        <v>76</v>
+      </c>
+      <c r="C21" s="3">
+        <v>15657.8203125</v>
       </c>
       <c r="D21">
-        <v>0.08</v>
+        <v>-4.41</v>
       </c>
       <c r="E21">
-        <v>0.96423528430107397</v>
+        <v>-41.796441292847298</v>
       </c>
       <c r="F21">
-        <v>0.18</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="G21">
-        <v>12.1124706484204</v>
+        <v>28.063777544089799</v>
       </c>
       <c r="H21">
         <v>0.96423528430107397</v>
@@ -1236,25 +1241,25 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>45379</v>
+        <v>45412</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22">
-        <v>100.709999084473</v>
+        <v>77</v>
+      </c>
+      <c r="C22" s="3">
+        <v>37815.921875</v>
       </c>
       <c r="D22">
-        <v>0.01</v>
+        <v>-5</v>
       </c>
       <c r="E22">
-        <v>0.120066022004939</v>
+        <v>-45.963991233736301</v>
       </c>
       <c r="F22">
-        <v>0.9</v>
+        <v>0.34</v>
       </c>
       <c r="G22">
-        <v>4.9386824398049098</v>
+        <v>10.903115305089401</v>
       </c>
       <c r="H22">
         <v>0.120066022004939</v>
@@ -1265,25 +1270,25 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>45379</v>
+        <v>45412</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23">
-        <v>128106.1</v>
+        <v>78</v>
+      </c>
+      <c r="C23" s="3">
+        <v>1973.91003417969</v>
       </c>
       <c r="D23">
-        <v>-0.71</v>
+        <v>-7.09</v>
       </c>
       <c r="E23">
-        <v>-8.1950436713639405</v>
+        <v>-58.623903040187201</v>
       </c>
       <c r="F23">
-        <v>-4.53</v>
+        <v>-2.62</v>
       </c>
       <c r="G23">
-        <v>29.6236428742214</v>
+        <v>11.5840137635918</v>
       </c>
       <c r="H23">
         <v>-8.1950436713639405</v>
@@ -1296,16 +1301,16 @@
       <c r="B24" t="s">
         <v>47</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="3">
         <v>10.75</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" t="s">
-        <v>49</v>
+        <v>79</v>
+      </c>
+      <c r="C25" s="3">
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>

--- a/Dados/fechamento_mes.xlsx
+++ b/Dados/fechamento_mes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capribr-my.sharepoint.com/personal/luizlopes_capribr_onmicrosoft_com/Documents/desempenho-ativos/Dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_FD14D649DF42729A60CED491CC6763CAFC6977FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FB5B5A1-837E-4A4F-877C-B3BECC9F1D75}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_FC14D649DF4244B265E7EC81BCA0794C8C286588" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="1455" windowWidth="19725" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="79">
   <si>
     <t>Dólar</t>
   </si>
@@ -176,7 +176,7 @@
     <t>Var% no ano</t>
   </si>
   <si>
-    <t>Número Índice</t>
+    <t>FFR (upper bound)</t>
   </si>
   <si>
     <t>Data</t>
@@ -185,6 +185,9 @@
     <t>Ativo</t>
   </si>
   <si>
+    <t>N�mero �ndice</t>
+  </si>
+  <si>
     <t>Var% no mes</t>
   </si>
   <si>
@@ -197,73 +200,67 @@
     <t>Var% em 12 meses</t>
   </si>
   <si>
+    <t>IXIC</t>
+  </si>
+  <si>
+    <t>RUT</t>
+  </si>
+  <si>
+    <t>SPX</t>
+  </si>
+  <si>
+    <t>TIP</t>
+  </si>
+  <si>
+    <t>AGG</t>
+  </si>
+  <si>
+    <t>IDA-IPCA Infraestrutura</t>
+  </si>
+  <si>
+    <t>HG</t>
+  </si>
+  <si>
+    <t>IMA-B</t>
+  </si>
+  <si>
+    <t>STIP</t>
+  </si>
+  <si>
+    <t>Idex-Infra Geral JGP</t>
+  </si>
+  <si>
+    <t>HY</t>
+  </si>
+  <si>
+    <t>IMA-B 5</t>
+  </si>
+  <si>
+    <t>IDA-DI</t>
+  </si>
+  <si>
+    <t>CDI</t>
+  </si>
+  <si>
+    <t>Idex-CDI Geral JGP</t>
+  </si>
+  <si>
+    <t>IRF-M</t>
+  </si>
+  <si>
+    <t>SGOV</t>
+  </si>
+  <si>
+    <t>IHFA</t>
+  </si>
+  <si>
     <t>Dólar</t>
   </si>
   <si>
+    <t>Ibovespa</t>
+  </si>
+  <si>
     <t>DXY</t>
-  </si>
-  <si>
-    <t>IDA-DI</t>
-  </si>
-  <si>
-    <t>Idex-CDI Geral JGP</t>
-  </si>
-  <si>
-    <t>CDI</t>
-  </si>
-  <si>
-    <t>SGOV</t>
-  </si>
-  <si>
-    <t>STIP</t>
-  </si>
-  <si>
-    <t>IMA-B 5</t>
-  </si>
-  <si>
-    <t>IRF-M</t>
-  </si>
-  <si>
-    <t>HY</t>
-  </si>
-  <si>
-    <t>IHFA</t>
-  </si>
-  <si>
-    <t>Idex-Infra Geral JGP</t>
-  </si>
-  <si>
-    <t>IMA-B</t>
-  </si>
-  <si>
-    <t>IDA-IPCA Infraestrutura</t>
-  </si>
-  <si>
-    <t>TIP</t>
-  </si>
-  <si>
-    <t>Ibovespa</t>
-  </si>
-  <si>
-    <t>HG</t>
-  </si>
-  <si>
-    <t>AGG</t>
-  </si>
-  <si>
-    <t>SPX</t>
-  </si>
-  <si>
-    <t>IXIC</t>
-  </si>
-  <si>
-    <t>DJI</t>
-  </si>
-  <si>
-    <t>RUT</t>
-  </si>
-  <si>
-    <t>FFR (upper bound)</t>
   </si>
 </sst>
 </file>
@@ -307,11 +304,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -621,7 +617,7 @@
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.140625" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -637,20 +633,20 @@
       <c r="B1" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>50</v>
+      <c r="C1" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="D1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H1" t="s">
         <v>48</v>
@@ -661,25 +657,25 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" s="3">
-        <v>5.1718000000000002</v>
+        <v>58</v>
+      </c>
+      <c r="C2" s="1">
+        <v>16735.01953125</v>
       </c>
       <c r="D2">
-        <v>3.51</v>
+        <v>6.88</v>
       </c>
       <c r="E2">
-        <v>51.282155230213597</v>
+        <v>122.206798176449</v>
       </c>
       <c r="F2">
-        <v>6.83</v>
+        <v>11.48</v>
       </c>
       <c r="G2">
-        <v>3.1266201395813198</v>
+        <v>29.374907564599798</v>
       </c>
       <c r="H2">
         <v>49.190930936488598</v>
@@ -690,25 +686,25 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="3">
-        <v>106.220001220703</v>
+        <v>59</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2070.1298828125</v>
       </c>
       <c r="D3">
-        <v>1.6</v>
+        <v>4.87</v>
       </c>
       <c r="E3">
-        <v>20.983040650908201</v>
+        <v>76.935597120785403</v>
       </c>
       <c r="F3" s="1">
-        <v>4.83</v>
+        <v>2.12</v>
       </c>
       <c r="G3">
-        <v>4.4752661883566498</v>
+        <v>18.316797869663201</v>
       </c>
       <c r="H3" s="1">
         <v>44.246067945403396</v>
@@ -719,25 +715,25 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="3">
-        <v>3583.856029</v>
+        <v>60</v>
+      </c>
+      <c r="C4" s="1">
+        <v>5277.509765625</v>
       </c>
       <c r="D4">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="E4">
-        <v>12.816456143923499</v>
+        <v>75.523549093701206</v>
       </c>
       <c r="F4" s="1">
-        <v>4.8099999999999996</v>
+        <v>10.64</v>
       </c>
       <c r="G4" s="1">
-        <v>16.9853047203942</v>
+        <v>26.2613471596528</v>
       </c>
       <c r="H4">
         <v>28.022981310051499</v>
@@ -748,25 +744,25 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>45411</v>
+        <v>45443</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1.78922946</v>
+        <v>15</v>
+      </c>
+      <c r="C5" s="1">
+        <v>38686.3203125</v>
       </c>
       <c r="D5">
-        <v>0.94</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E5">
-        <v>11.881841195515699</v>
+        <v>31.373449839960099</v>
       </c>
       <c r="F5">
-        <v>4.95</v>
+        <v>2.64</v>
       </c>
       <c r="G5">
-        <v>17.590183061214301</v>
+        <v>17.558051102514099</v>
       </c>
       <c r="H5">
         <v>23.726113884365802</v>
@@ -777,25 +773,25 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="3">
-        <v>3198.6491236259999</v>
+      <c r="C6" s="1">
+        <v>106.699996948242</v>
       </c>
       <c r="D6">
-        <v>0.89</v>
+        <v>1.78</v>
       </c>
       <c r="E6">
-        <v>11.2186103609413</v>
+        <v>23.580332236181299</v>
       </c>
       <c r="F6">
-        <v>3.54</v>
+        <v>-0.02</v>
       </c>
       <c r="G6">
-        <v>12.385098482992801</v>
+        <v>1.35974166256458</v>
       </c>
       <c r="H6">
         <v>15.2527113059203</v>
@@ -806,25 +802,25 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="3">
-        <v>100.27199554443401</v>
+      <c r="C7" s="1">
+        <v>96.519996643066406</v>
       </c>
       <c r="D7">
-        <v>0.44</v>
+        <v>1.67</v>
       </c>
       <c r="E7">
-        <v>5.40966873236182</v>
+        <v>21.987093185571101</v>
       </c>
       <c r="F7">
-        <v>1.34</v>
+        <v>-1.87</v>
       </c>
       <c r="G7">
-        <v>4.9989929792960197</v>
+        <v>1.0159267495996001</v>
       </c>
       <c r="H7">
         <v>14.8433488405669</v>
@@ -835,25 +831,25 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>45412</v>
+        <v>45442</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="3">
-        <v>98.568000793457003</v>
+        <v>64</v>
+      </c>
+      <c r="C8" s="1">
+        <v>3206.95</v>
       </c>
       <c r="D8">
-        <v>-0.17</v>
+        <v>1.46</v>
       </c>
       <c r="E8">
-        <v>-2.0210336736933998</v>
+        <v>18.997625578845899</v>
       </c>
       <c r="F8">
-        <v>0.68</v>
+        <v>-0.99</v>
       </c>
       <c r="G8">
-        <v>2.8005878636553101</v>
+        <v>4.8691159398963597</v>
       </c>
       <c r="H8">
         <v>14.8433488405669</v>
@@ -864,25 +860,25 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" s="3">
-        <v>9142.7225539999999</v>
+        <v>76</v>
+      </c>
+      <c r="C9" s="1">
+        <v>5.2416</v>
       </c>
       <c r="D9">
-        <v>-0.2</v>
+        <v>1.35</v>
       </c>
       <c r="E9">
-        <v>-2.3737752105284899</v>
+        <v>17.458658475004299</v>
       </c>
       <c r="F9">
-        <v>1.85</v>
+        <v>8.27</v>
       </c>
       <c r="G9">
-        <v>8.3152877595076298</v>
+        <v>4.9285342515114303</v>
       </c>
       <c r="H9">
         <v>14.7071911538915</v>
@@ -893,25 +889,25 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>45412</v>
+        <v>45441</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="3">
-        <v>18148.423220000001</v>
+        <v>63</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2163.7092259999999</v>
       </c>
       <c r="D10">
-        <v>-0.52</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E10">
-        <v>-6.06459348280368</v>
+        <v>14.4353196047725</v>
       </c>
       <c r="F10">
-        <v>1.1399999999999999</v>
+        <v>3.07</v>
       </c>
       <c r="G10">
-        <v>12.016316962550899</v>
+        <v>12.447151499807701</v>
       </c>
       <c r="H10">
         <v>10.4274913828344</v>
@@ -922,25 +918,25 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>45412</v>
+        <v>45441</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1598.18</v>
+        <v>65</v>
+      </c>
+      <c r="C11" s="1">
+        <v>9870.5574309999993</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="E11">
-        <v>-11.361512828387101</v>
+        <v>13.893347713220299</v>
       </c>
       <c r="F11">
-        <v>0.49</v>
+        <v>-0.37</v>
       </c>
       <c r="G11">
-        <v>9.3625116329993894</v>
+        <v>6.4372401941176003</v>
       </c>
       <c r="H11">
         <v>9.6415338967120103</v>
@@ -951,25 +947,25 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>45408</v>
+        <v>45443</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="3">
-        <v>5000.43</v>
+        <v>66</v>
+      </c>
+      <c r="C12" s="1">
+        <v>99.569999694824205</v>
       </c>
       <c r="D12">
-        <v>-1.05</v>
+        <v>1.02</v>
       </c>
       <c r="E12">
-        <v>-11.8972260598385</v>
+        <v>12.9505552292121</v>
       </c>
       <c r="F12">
-        <v>-0.38</v>
+        <v>1.71</v>
       </c>
       <c r="G12">
-        <v>7.1662326807470098</v>
+        <v>4.5067123829450697</v>
       </c>
       <c r="H12">
         <v>8.2139158364711307</v>
@@ -980,25 +976,25 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>45411</v>
+        <v>45441</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="3">
-        <v>1.3198431500000001</v>
+        <v>69</v>
+      </c>
+      <c r="C13" s="1">
+        <v>9228.9452390000006</v>
       </c>
       <c r="D13">
-        <v>-1.19</v>
+        <v>0.94</v>
       </c>
       <c r="E13">
-        <v>-13.3814734952748</v>
+        <v>11.881841195515699</v>
       </c>
       <c r="F13">
         <v>2.81</v>
       </c>
       <c r="G13">
-        <v>15.833515836683199</v>
+        <v>8.9221900379494308</v>
       </c>
       <c r="H13">
         <v>8.0849810365515502</v>
@@ -1009,25 +1005,25 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>45412</v>
+        <v>45442</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="3">
-        <v>9764.2466420000001</v>
+        <v>68</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1613.09</v>
       </c>
       <c r="D14">
-        <v>-1.61</v>
+        <v>0.93</v>
       </c>
       <c r="E14">
-        <v>-17.697784373517798</v>
+        <v>11.748905709858199</v>
       </c>
       <c r="F14">
-        <v>-1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G14">
-        <v>7.6248588742959997</v>
+        <v>9.4236078606944904</v>
       </c>
       <c r="H14">
         <v>7.5706487926186803</v>
@@ -1038,25 +1034,25 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>45412</v>
+        <v>45441</v>
       </c>
       <c r="B15" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="3">
-        <v>2139.6358599999999</v>
+      <c r="C15" s="1">
+        <v>3616.6198169999998</v>
       </c>
       <c r="D15">
-        <v>-1.68</v>
+        <v>0.91</v>
       </c>
       <c r="E15">
-        <v>-18.397692706630799</v>
+        <v>11.483469003274401</v>
       </c>
       <c r="F15">
-        <v>1.92</v>
+        <v>5.77</v>
       </c>
       <c r="G15">
-        <v>14.661723748123</v>
+        <v>16.525664018257299</v>
       </c>
       <c r="H15">
         <v>7.0585609779296297</v>
@@ -1067,25 +1063,25 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="3">
-        <v>105.529998779297</v>
+      <c r="C16" s="1">
+        <v>3225.3046890274099</v>
       </c>
       <c r="D16">
-        <v>-1.69</v>
+        <v>0.83</v>
       </c>
       <c r="E16">
-        <v>-18.497232992970702</v>
+        <v>10.4274913828344</v>
       </c>
       <c r="F16">
-        <v>-1.76</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="G16">
-        <v>-1.60115483246061</v>
+        <v>12.119741836678701</v>
       </c>
       <c r="H16">
         <v>6.6759626640876801</v>
@@ -1096,25 +1092,25 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>45412</v>
+        <v>45441</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="3">
-        <v>125924.19</v>
+        <v>67</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1.32660003</v>
       </c>
       <c r="D17">
-        <v>-1.7</v>
+        <v>0.83</v>
       </c>
       <c r="E17">
-        <v>-18.596661965019202</v>
+        <v>10.4274913828344</v>
       </c>
       <c r="F17">
-        <v>-6.16</v>
+        <v>3.33</v>
       </c>
       <c r="G17">
-        <v>22.347590647832899</v>
+        <v>12.666394719358699</v>
       </c>
       <c r="H17">
         <v>6.5487086851492098</v>
@@ -1125,25 +1121,25 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>45412</v>
+        <v>45441</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="3">
-        <v>3160.95</v>
+        <v>72</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1.8054450099999999</v>
       </c>
       <c r="D18">
-        <v>-2.33</v>
+        <v>0.8</v>
       </c>
       <c r="E18">
-        <v>-24.641151689780699</v>
+        <v>10.0338693716146</v>
       </c>
       <c r="F18">
-        <v>-2.41</v>
+        <v>5.91</v>
       </c>
       <c r="G18">
-        <v>2.06028787849448</v>
+        <v>16.649021040034299</v>
       </c>
       <c r="H18">
         <v>5.9145235035986001</v>
@@ -1154,25 +1150,25 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B19" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="3">
-        <v>94.935005187988295</v>
+      <c r="C19" s="1">
+        <v>100.75</v>
       </c>
       <c r="D19">
-        <v>-2.48</v>
+        <v>0.48</v>
       </c>
       <c r="E19">
-        <v>-26.018299194832501</v>
+        <v>5.9145235035986001</v>
       </c>
       <c r="F19">
-        <v>-3.48</v>
+        <v>1.82</v>
       </c>
       <c r="G19">
-        <v>-1.77983637762208</v>
+        <v>5.05692348424658</v>
       </c>
       <c r="H19">
         <v>4.53147769825524</v>
@@ -1183,25 +1179,25 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>45412</v>
+        <v>45441</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" s="3">
-        <v>5035.68994140625</v>
+        <v>73</v>
+      </c>
+      <c r="C20" s="1">
+        <v>18231.434233</v>
       </c>
       <c r="D20">
-        <v>-4.16</v>
+        <v>0.46</v>
       </c>
       <c r="E20">
-        <v>-39.943272941690303</v>
+        <v>5.6618197194086903</v>
       </c>
       <c r="F20">
-        <v>5.57</v>
+        <v>1.61</v>
       </c>
       <c r="G20">
-        <v>20.775011871866798</v>
+        <v>10.454736122629299</v>
       </c>
       <c r="H20">
         <v>3.1650049434697798</v>
@@ -1212,25 +1208,25 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>45412</v>
+        <v>45439</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" s="3">
-        <v>15657.8203125</v>
+        <v>75</v>
+      </c>
+      <c r="C21" s="1">
+        <v>4994.6000000000004</v>
       </c>
       <c r="D21">
-        <v>-4.41</v>
+        <v>0.33</v>
       </c>
       <c r="E21">
-        <v>-41.796441292847298</v>
+        <v>4.0326705154239502</v>
       </c>
       <c r="F21">
-        <v>4.3099999999999996</v>
+        <v>-0.5</v>
       </c>
       <c r="G21">
-        <v>28.063777544089799</v>
+        <v>6.3318842369249904</v>
       </c>
       <c r="H21">
         <v>0.96423528430107397</v>
@@ -1241,25 +1237,25 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" s="3">
-        <v>37815.921875</v>
+        <v>78</v>
+      </c>
+      <c r="C22" s="1">
+        <v>104.669998168945</v>
       </c>
       <c r="D22">
-        <v>-5</v>
+        <v>-1.46</v>
       </c>
       <c r="E22">
-        <v>-45.963991233736301</v>
+        <v>-16.179413507406998</v>
       </c>
       <c r="F22">
-        <v>0.34</v>
+        <v>3.3</v>
       </c>
       <c r="G22">
-        <v>10.903115305089401</v>
+        <v>0.33550467326002298</v>
       </c>
       <c r="H22">
         <v>0.120066022004939</v>
@@ -1270,25 +1266,25 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" s="3">
-        <v>1973.91003417969</v>
+        <v>77</v>
+      </c>
+      <c r="C23" s="1">
+        <v>122098.09</v>
       </c>
       <c r="D23">
-        <v>-7.09</v>
+        <v>-3.04</v>
       </c>
       <c r="E23">
-        <v>-58.623903040187201</v>
+        <v>-30.958330923473302</v>
       </c>
       <c r="F23">
-        <v>-2.62</v>
+        <v>-9.01</v>
       </c>
       <c r="G23">
-        <v>11.5840137635918</v>
+        <v>10.662854584378</v>
       </c>
       <c r="H23">
         <v>-8.1950436713639405</v>
@@ -1301,15 +1297,15 @@
       <c r="B24" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="1">
         <v>10.75</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" s="3">
+        <v>50</v>
+      </c>
+      <c r="C25" s="1">
         <v>5.5</v>
       </c>
     </row>

--- a/Dados/fechamento_mes.xlsx
+++ b/Dados/fechamento_mes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capribr-my.sharepoint.com/personal/luizlopes_capribr_onmicrosoft_com/Documents/desempenho-ativos/Dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_FC14D649DF4244B265E7EC81BCA0794C8C286588" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_FD14D649DF42AB8AA6E34078DCA25F20F5E9404A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F192B3C-45C8-411F-BF8C-88CE1EF1C101}"/>
   <bookViews>
-    <workbookView xWindow="6120" yWindow="1455" windowWidth="19725" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fechamento" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="80">
   <si>
     <t>Dólar</t>
   </si>
@@ -179,15 +179,15 @@
     <t>FFR (upper bound)</t>
   </si>
   <si>
+    <t>Número Índice</t>
+  </si>
+  <si>
     <t>Data</t>
   </si>
   <si>
     <t>Ativo</t>
   </si>
   <si>
-    <t>N�mero �ndice</t>
-  </si>
-  <si>
     <t>Var% no mes</t>
   </si>
   <si>
@@ -200,67 +200,70 @@
     <t>Var% em 12 meses</t>
   </si>
   <si>
+    <t>Dólar</t>
+  </si>
+  <si>
     <t>IXIC</t>
   </si>
   <si>
+    <t>SPX</t>
+  </si>
+  <si>
+    <t>Ibovespa</t>
+  </si>
+  <si>
+    <t>DXY</t>
+  </si>
+  <si>
+    <t>DJI</t>
+  </si>
+  <si>
+    <t>Idex-CDI Geral JGP</t>
+  </si>
+  <si>
+    <t>HG</t>
+  </si>
+  <si>
+    <t>IDA-DI</t>
+  </si>
+  <si>
+    <t>HY</t>
+  </si>
+  <si>
+    <t>AGG</t>
+  </si>
+  <si>
+    <t>CDI</t>
+  </si>
+  <si>
+    <t>TIP</t>
+  </si>
+  <si>
+    <t>STIP</t>
+  </si>
+  <si>
+    <t>IHFA</t>
+  </si>
+  <si>
+    <t>SGOV</t>
+  </si>
+  <si>
+    <t>IMA-B 5</t>
+  </si>
+  <si>
+    <t>IDA-IPCA Infraestrutura</t>
+  </si>
+  <si>
+    <t>Idex-Infra Geral JGP</t>
+  </si>
+  <si>
+    <t>IRF-M</t>
+  </si>
+  <si>
+    <t>IMA-B</t>
+  </si>
+  <si>
     <t>RUT</t>
-  </si>
-  <si>
-    <t>SPX</t>
-  </si>
-  <si>
-    <t>TIP</t>
-  </si>
-  <si>
-    <t>AGG</t>
-  </si>
-  <si>
-    <t>IDA-IPCA Infraestrutura</t>
-  </si>
-  <si>
-    <t>HG</t>
-  </si>
-  <si>
-    <t>IMA-B</t>
-  </si>
-  <si>
-    <t>STIP</t>
-  </si>
-  <si>
-    <t>Idex-Infra Geral JGP</t>
-  </si>
-  <si>
-    <t>HY</t>
-  </si>
-  <si>
-    <t>IMA-B 5</t>
-  </si>
-  <si>
-    <t>IDA-DI</t>
-  </si>
-  <si>
-    <t>CDI</t>
-  </si>
-  <si>
-    <t>Idex-CDI Geral JGP</t>
-  </si>
-  <si>
-    <t>IRF-M</t>
-  </si>
-  <si>
-    <t>SGOV</t>
-  </si>
-  <si>
-    <t>IHFA</t>
-  </si>
-  <si>
-    <t>Dólar</t>
-  </si>
-  <si>
-    <t>Ibovespa</t>
-  </si>
-  <si>
-    <t>DXY</t>
   </si>
 </sst>
 </file>
@@ -628,13 +631,13 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="D1" t="s">
         <v>54</v>
@@ -657,25 +660,25 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>45443</v>
+        <v>45471</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
       </c>
       <c r="C2" s="1">
-        <v>16735.01953125</v>
+        <v>5.5589000000000004</v>
       </c>
       <c r="D2">
-        <v>6.88</v>
+        <v>6.05</v>
       </c>
       <c r="E2">
-        <v>122.206798176449</v>
+        <v>102.361585868257</v>
       </c>
       <c r="F2">
-        <v>11.48</v>
+        <v>14.82</v>
       </c>
       <c r="G2">
-        <v>29.374907564599798</v>
+        <v>16.044924117487401</v>
       </c>
       <c r="H2">
         <v>49.190930936488598</v>
@@ -686,25 +689,25 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>45443</v>
+        <v>45471</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
       </c>
       <c r="C3" s="1">
-        <v>2070.1298828125</v>
+        <v>17732.599609375</v>
       </c>
       <c r="D3">
-        <v>4.87</v>
+        <v>5.96</v>
       </c>
       <c r="E3">
-        <v>76.935597120785403</v>
+        <v>100.310352633954</v>
       </c>
       <c r="F3" s="1">
-        <v>2.12</v>
+        <v>18.13</v>
       </c>
       <c r="G3">
-        <v>18.316797869663201</v>
+        <v>30.4659047538028</v>
       </c>
       <c r="H3" s="1">
         <v>44.246067945403396</v>
@@ -715,25 +718,25 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>45443</v>
+        <v>45471</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="1">
-        <v>5277.509765625</v>
+        <v>5460.47998046875</v>
       </c>
       <c r="D4">
-        <v>4.8</v>
+        <v>3.47</v>
       </c>
       <c r="E4">
-        <v>75.523549093701206</v>
+        <v>50.582113723059202</v>
       </c>
       <c r="F4" s="1">
-        <v>10.64</v>
+        <v>14.48</v>
       </c>
       <c r="G4" s="1">
-        <v>26.2613471596528</v>
+        <v>24.7579349359183</v>
       </c>
       <c r="H4">
         <v>28.022981310051499</v>
@@ -744,25 +747,25 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>45443</v>
+        <v>45471</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="C5" s="1">
-        <v>38686.3203125</v>
+        <v>123906.55</v>
       </c>
       <c r="D5">
-        <v>2.2999999999999998</v>
+        <v>1.48</v>
       </c>
       <c r="E5">
-        <v>31.373449839960099</v>
+        <v>19.279415582807701</v>
       </c>
       <c r="F5">
-        <v>2.64</v>
+        <v>-7.66</v>
       </c>
       <c r="G5">
-        <v>17.558051102514099</v>
+        <v>5.4318619005816204</v>
       </c>
       <c r="H5">
         <v>23.726113884365802</v>
@@ -773,25 +776,25 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>45443</v>
+        <v>45471</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="1">
-        <v>106.699996948242</v>
+        <v>105.870002746582</v>
       </c>
       <c r="D6">
-        <v>1.78</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="E6">
-        <v>23.580332236181299</v>
+        <v>14.7071911538915</v>
       </c>
       <c r="F6">
-        <v>-0.02</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="G6">
-        <v>1.35974166256458</v>
+        <v>2.87629868733783</v>
       </c>
       <c r="H6">
         <v>15.2527113059203</v>
@@ -802,25 +805,25 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>45443</v>
+        <v>45471</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" s="1">
-        <v>96.519996643066406</v>
+        <v>39118.859375</v>
       </c>
       <c r="D7">
-        <v>1.67</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="E7">
-        <v>21.987093185571101</v>
+        <v>14.2996054499739</v>
       </c>
       <c r="F7">
-        <v>-1.87</v>
+        <v>3.79</v>
       </c>
       <c r="G7">
-        <v>1.0159267495996001</v>
+        <v>15.5562345601301</v>
       </c>
       <c r="H7">
         <v>14.8433488405669</v>
@@ -831,25 +834,25 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>45442</v>
+        <v>45470</v>
       </c>
       <c r="B8" t="s">
         <v>64</v>
       </c>
       <c r="C8" s="1">
-        <v>3206.95</v>
+        <v>1.82708457</v>
       </c>
       <c r="D8">
-        <v>1.46</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="E8">
-        <v>18.997625578845899</v>
+        <v>14.164038846995799</v>
       </c>
       <c r="F8">
-        <v>-0.99</v>
+        <v>7.17</v>
       </c>
       <c r="G8">
-        <v>4.8691159398963597</v>
+        <v>16.403510177461001</v>
       </c>
       <c r="H8">
         <v>14.8433488405669</v>
@@ -860,25 +863,25 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>45443</v>
+        <v>45470</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C9" s="1">
-        <v>5.2416</v>
+        <v>3254.63</v>
       </c>
       <c r="D9">
-        <v>1.35</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="E9">
-        <v>17.458658475004299</v>
+        <v>13.893347713220299</v>
       </c>
       <c r="F9">
-        <v>8.27</v>
+        <v>0.49</v>
       </c>
       <c r="G9">
-        <v>4.9285342515114303</v>
+        <v>6.2965406422282202</v>
       </c>
       <c r="H9">
         <v>14.7071911538915</v>
@@ -889,25 +892,25 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>45441</v>
+        <v>45470</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C10" s="1">
-        <v>2163.7092259999999</v>
+        <v>3654.7325860000001</v>
       </c>
       <c r="D10">
-        <v>1.1299999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="E10">
-        <v>14.4353196047725</v>
+        <v>12.816456143923499</v>
       </c>
       <c r="F10">
-        <v>3.07</v>
+        <v>6.89</v>
       </c>
       <c r="G10">
-        <v>12.447151499807701</v>
+        <v>16.1573101256195</v>
       </c>
       <c r="H10">
         <v>10.4274913828344</v>
@@ -918,25 +921,25 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>45441</v>
+        <v>45470</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C11" s="1">
-        <v>9870.5574309999993</v>
+        <v>1630.94</v>
       </c>
       <c r="D11">
-        <v>1.0900000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="E11">
-        <v>13.893347713220299</v>
+        <v>11.350967495666801</v>
       </c>
       <c r="F11">
-        <v>-0.37</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="G11">
-        <v>6.4372401941176003</v>
+        <v>10.4845647858987</v>
       </c>
       <c r="H11">
         <v>9.6415338967120103</v>
@@ -947,25 +950,25 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>45443</v>
+        <v>45471</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C12" s="1">
-        <v>99.569999694824205</v>
+        <v>97.069999694824205</v>
       </c>
       <c r="D12">
-        <v>1.02</v>
+        <v>0.89</v>
       </c>
       <c r="E12">
-        <v>12.9505552292121</v>
+        <v>11.2186103609413</v>
       </c>
       <c r="F12">
-        <v>1.71</v>
+        <v>-0.71</v>
       </c>
       <c r="G12">
-        <v>4.5067123829450697</v>
+        <v>2.0363303500997798</v>
       </c>
       <c r="H12">
         <v>8.2139158364711307</v>
@@ -976,25 +979,25 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>45441</v>
+        <v>45471</v>
       </c>
       <c r="B13" t="s">
         <v>69</v>
       </c>
       <c r="C13" s="1">
-        <v>9228.9452390000006</v>
+        <v>3250.7306934221501</v>
       </c>
       <c r="D13">
-        <v>0.94</v>
+        <v>0.79</v>
       </c>
       <c r="E13">
-        <v>11.881841195515699</v>
+        <v>9.9029481205437797</v>
       </c>
       <c r="F13">
-        <v>2.81</v>
+        <v>5.22</v>
       </c>
       <c r="G13">
-        <v>8.9221900379494308</v>
+        <v>11.861866090733001</v>
       </c>
       <c r="H13">
         <v>8.0849810365515502</v>
@@ -1005,25 +1008,25 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>45442</v>
+        <v>45471</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C14" s="1">
-        <v>1613.09</v>
+        <v>106.779998779297</v>
       </c>
       <c r="D14">
-        <v>0.93</v>
+        <v>0.76</v>
       </c>
       <c r="E14">
-        <v>11.748905709858199</v>
+        <v>9.5110406408293695</v>
       </c>
       <c r="F14">
-        <v>1.43</v>
+        <v>0.74</v>
       </c>
       <c r="G14">
-        <v>9.4236078606944904</v>
+        <v>2.2518710310908099</v>
       </c>
       <c r="H14">
         <v>7.5706487926186803</v>
@@ -1034,25 +1037,25 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>45441</v>
+        <v>45471</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" s="1">
-        <v>3616.6198169999998</v>
+        <v>99.489997863769503</v>
       </c>
       <c r="D15">
-        <v>0.91</v>
+        <v>0.59</v>
       </c>
       <c r="E15">
-        <v>11.483469003274401</v>
+        <v>7.3143248890742898</v>
       </c>
       <c r="F15">
-        <v>5.77</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="G15">
-        <v>16.525664018257299</v>
+        <v>5.1700995629026201</v>
       </c>
       <c r="H15">
         <v>7.0585609779296297</v>
@@ -1063,25 +1066,25 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>45443</v>
+        <v>45468</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="1">
-        <v>3225.3046890274099</v>
+        <v>5019.12</v>
       </c>
       <c r="D16">
-        <v>0.83</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E16">
-        <v>10.4274913828344</v>
+        <v>6.8033559467648397</v>
       </c>
       <c r="F16">
-        <v>4.4000000000000004</v>
+        <v>-0.01</v>
       </c>
       <c r="G16">
-        <v>12.119741836678701</v>
+        <v>5.2255092906094802</v>
       </c>
       <c r="H16">
         <v>6.6759626640876801</v>
@@ -1092,25 +1095,25 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>45441</v>
+        <v>45471</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C17" s="1">
-        <v>1.32660003</v>
+        <v>100.709999084473</v>
       </c>
       <c r="D17">
-        <v>0.83</v>
+        <v>0.4</v>
       </c>
       <c r="E17">
-        <v>10.4274913828344</v>
+        <v>4.9070207534805697</v>
       </c>
       <c r="F17">
-        <v>3.33</v>
+        <v>2.65</v>
       </c>
       <c r="G17">
-        <v>12.666394719358699</v>
+        <v>5.4522193059222799</v>
       </c>
       <c r="H17">
         <v>6.5487086851492098</v>
@@ -1121,25 +1124,25 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>45441</v>
+        <v>45471</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C18" s="1">
-        <v>1.8054450099999999</v>
+        <v>9274.9067020000002</v>
       </c>
       <c r="D18">
-        <v>0.8</v>
+        <v>0.39</v>
       </c>
       <c r="E18">
-        <v>10.0338693716146</v>
+        <v>4.7817025413167604</v>
       </c>
       <c r="F18">
-        <v>5.91</v>
+        <v>3.32</v>
       </c>
       <c r="G18">
-        <v>16.649021040034299</v>
+        <v>8.4391317864746593</v>
       </c>
       <c r="H18">
         <v>5.9145235035986001</v>
@@ -1150,25 +1153,25 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>45443</v>
+        <v>45470</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" s="1">
-        <v>100.75</v>
+        <v>2163.3704269999998</v>
       </c>
       <c r="D19">
-        <v>0.48</v>
+        <v>-0.24</v>
       </c>
       <c r="E19">
-        <v>5.9145235035986001</v>
+        <v>-2.8422864919975299</v>
       </c>
       <c r="F19">
-        <v>1.82</v>
+        <v>3.06</v>
       </c>
       <c r="G19">
-        <v>5.05692348424658</v>
+        <v>9.7501393330649702</v>
       </c>
       <c r="H19">
         <v>4.53147769825524</v>
@@ -1179,25 +1182,25 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>45441</v>
+        <v>45470</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C20" s="1">
-        <v>18231.434233</v>
+        <v>1.3262792000000001</v>
       </c>
       <c r="D20">
-        <v>0.46</v>
+        <v>-0.28000000000000003</v>
       </c>
       <c r="E20">
-        <v>5.6618197194086903</v>
+        <v>-3.3087359150390201</v>
       </c>
       <c r="F20">
-        <v>1.61</v>
+        <v>3.31</v>
       </c>
       <c r="G20">
-        <v>10.454736122629299</v>
+        <v>9.7698021708244198</v>
       </c>
       <c r="H20">
         <v>3.1650049434697798</v>
@@ -1208,25 +1211,25 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>45439</v>
+        <v>45471</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C21" s="1">
-        <v>4994.6000000000004</v>
+        <v>18213.783502999999</v>
       </c>
       <c r="D21">
-        <v>0.33</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="E21">
-        <v>4.0326705154239502</v>
+        <v>-3.42502707314907</v>
       </c>
       <c r="F21">
-        <v>-0.5</v>
+        <v>1.51</v>
       </c>
       <c r="G21">
-        <v>6.3318842369249904</v>
+        <v>8.3301007386410202</v>
       </c>
       <c r="H21">
         <v>0.96423528430107397</v>
@@ -1237,25 +1240,25 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>45443</v>
+        <v>45471</v>
       </c>
       <c r="B22" t="s">
         <v>78</v>
       </c>
       <c r="C22" s="1">
-        <v>104.669998168945</v>
+        <v>9798.3126709999997</v>
       </c>
       <c r="D22">
-        <v>-1.46</v>
+        <v>-0.97</v>
       </c>
       <c r="E22">
-        <v>-16.179413507406998</v>
+        <v>-11.038653310901999</v>
       </c>
       <c r="F22">
-        <v>3.3</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="G22">
-        <v>0.33550467326002298</v>
+        <v>3.9334380014737902</v>
       </c>
       <c r="H22">
         <v>0.120066022004939</v>
@@ -1266,25 +1269,25 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>45443</v>
+        <v>45471</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C23" s="1">
-        <v>122098.09</v>
+        <v>2047.68994140625</v>
       </c>
       <c r="D23">
-        <v>-3.04</v>
+        <v>-1.08</v>
       </c>
       <c r="E23">
-        <v>-30.958330923473302</v>
+        <v>-12.217227713764199</v>
       </c>
       <c r="F23">
-        <v>-9.01</v>
+        <v>1.02</v>
       </c>
       <c r="G23">
-        <v>10.662854584378</v>
+        <v>10.1672657079554</v>
       </c>
       <c r="H23">
         <v>-8.1950436713639405</v>
@@ -1298,7 +1301,7 @@
         <v>47</v>
       </c>
       <c r="C24" s="1">
-        <v>10.75</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">

--- a/Dados/fechamento_mes.xlsx
+++ b/Dados/fechamento_mes.xlsx
@@ -1,20 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capribr-my.sharepoint.com/personal/luizlopes_capribr_onmicrosoft_com/Documents/desempenho-ativos/Dados/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_FD14D649DF42AB8AA6E34078DCA25F20F5E9404A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F192B3C-45C8-411F-BF8C-88CE1EF1C101}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Fechamento" sheetId="1" r:id="rId1"/>
-    <sheet name="Glossário" sheetId="2" r:id="rId2"/>
+    <sheet name="Fechamento" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Glossário" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fechamento!$A$1:$D$21</definedName>
@@ -24,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t>Dólar</t>
   </si>
@@ -264,6 +257,93 @@
   </si>
   <si>
     <t>RUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N�mero �ndice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Var% no mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Var% no mes anualizado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Var% no ano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Var% em 12 meses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ibovespa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IXIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DJI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMA-B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDA-IPCA Infraestrutura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRF-M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idex-Infra Geral JGP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMA-B 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IHFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDA-DI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idex-CDI Geral JGP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGOV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DXY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dólar</t>
   </si>
 </sst>
 </file>
@@ -271,9 +351,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,8 +389,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -614,42 +694,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="8" width="22.85546875" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="22.85546875" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="12" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="D1" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="G1" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="H1" t="s">
         <v>48</v>
@@ -658,657 +738,657 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>45471</v>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>45485</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="1">
-        <v>5.5589000000000004</v>
-      </c>
-      <c r="D2">
-        <v>6.05</v>
-      </c>
-      <c r="E2">
-        <v>102.361585868257</v>
-      </c>
-      <c r="F2">
-        <v>14.82</v>
-      </c>
-      <c r="G2">
-        <v>16.044924117487401</v>
-      </c>
-      <c r="H2">
+        <v>87</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>2148.27001953125</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="E2" t="n">
+        <v>77.7471493338375</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="G2" t="n">
+        <v>11.1147324429613</v>
+      </c>
+      <c r="H2" t="n">
         <v>49.190930936488598</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>4.8099999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>45471</v>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45485</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="1">
-        <v>17732.599609375</v>
-      </c>
-      <c r="D3">
-        <v>5.96</v>
-      </c>
-      <c r="E3">
-        <v>100.310352633954</v>
-      </c>
-      <c r="F3" s="1">
-        <v>18.13</v>
-      </c>
-      <c r="G3">
-        <v>30.4659047538028</v>
-      </c>
-      <c r="H3" s="1">
+        <v>88</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>128896.98</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="E3" t="n">
+        <v>60.6583054281429</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>-3.94</v>
+      </c>
+      <c r="G3" t="n">
+        <v>9.64774771954571</v>
+      </c>
+      <c r="H3" s="1" t="n">
         <v>44.246067945403396</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>10.16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>45471</v>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45485</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="1">
-        <v>5460.47998046875</v>
-      </c>
-      <c r="D4">
-        <v>3.47</v>
-      </c>
-      <c r="E4">
-        <v>50.582113723059202</v>
-      </c>
-      <c r="F4" s="1">
-        <v>14.48</v>
-      </c>
-      <c r="G4" s="1">
-        <v>24.7579349359183</v>
-      </c>
-      <c r="H4">
+        <v>89</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>18398.44921875</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E4" t="n">
+        <v>55.5454331372475</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>32.1826434617517</v>
+      </c>
+      <c r="H4" t="n">
         <v>28.022981310051499</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>5.62</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>45471</v>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45485</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="1">
-        <v>123906.55</v>
-      </c>
-      <c r="D5">
-        <v>1.48</v>
-      </c>
-      <c r="E5">
-        <v>19.279415582807701</v>
-      </c>
-      <c r="F5">
-        <v>-7.66</v>
-      </c>
-      <c r="G5">
-        <v>5.4318619005816204</v>
-      </c>
-      <c r="H5">
+        <v>90</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>5615.35009765625</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E5" t="n">
+        <v>39.9409492981759</v>
+      </c>
+      <c r="F5" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="G5" t="n">
+        <v>25.562365869402</v>
+      </c>
+      <c r="H5" t="n">
         <v>23.726113884365802</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>9.11</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>45471</v>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45485</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="1">
-        <v>105.870002746582</v>
-      </c>
-      <c r="D6">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="E6">
+        <v>91</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>40000.8984375</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E6" t="n">
+        <v>30.6049989887568</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="G6" t="n">
+        <v>16.4596559376826</v>
+      </c>
+      <c r="H6" t="n">
+        <v>15.2527113059203</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45485</v>
+      </c>
+      <c r="B7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>10009.728844</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="E7" t="n">
+        <v>29.2321623313199</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.64820829803443</v>
+      </c>
+      <c r="H7" t="n">
+        <v>14.8433488405669</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45484</v>
+      </c>
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>2194.866737</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="E8" t="n">
+        <v>24.8980546006235</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10.4870036025003</v>
+      </c>
+      <c r="H8" t="n">
+        <v>14.8433488405669</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45485</v>
+      </c>
+      <c r="B9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>3295.65</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E9" t="n">
+        <v>22.7089438137531</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.94953756287526</v>
+      </c>
+      <c r="H9" t="n">
         <v>14.7071911538915</v>
       </c>
-      <c r="F6">
-        <v>4.4800000000000004</v>
-      </c>
-      <c r="G6">
-        <v>2.87629868733783</v>
-      </c>
-      <c r="H6">
-        <v>15.2527113059203</v>
-      </c>
-      <c r="I6">
-        <v>3.96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>45471</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="1">
-        <v>39118.859375</v>
-      </c>
-      <c r="D7">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="E7">
-        <v>14.2996054499739</v>
-      </c>
-      <c r="F7">
-        <v>3.79</v>
-      </c>
-      <c r="G7">
-        <v>15.5562345601301</v>
-      </c>
-      <c r="H7">
-        <v>14.8433488405669</v>
-      </c>
-      <c r="I7">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>45470</v>
-      </c>
-      <c r="B8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1.82708457</v>
-      </c>
-      <c r="D8">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="E8">
-        <v>14.164038846995799</v>
-      </c>
-      <c r="F8">
-        <v>7.17</v>
-      </c>
-      <c r="G8">
-        <v>16.403510177461001</v>
-      </c>
-      <c r="H8">
-        <v>14.8433488405669</v>
-      </c>
-      <c r="I8">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>45470</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="1">
-        <v>3254.63</v>
-      </c>
-      <c r="D9">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="E9">
-        <v>13.893347713220299</v>
-      </c>
-      <c r="F9">
-        <v>0.49</v>
-      </c>
-      <c r="G9">
-        <v>6.2965406422282202</v>
-      </c>
-      <c r="H9">
-        <v>14.7071911538915</v>
-      </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>3.75</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>45470</v>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45485</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="1">
-        <v>3654.7325860000001</v>
-      </c>
-      <c r="D10">
-        <v>1.01</v>
-      </c>
-      <c r="E10">
-        <v>12.816456143923499</v>
-      </c>
-      <c r="F10">
-        <v>6.89</v>
-      </c>
-      <c r="G10">
-        <v>16.1573101256195</v>
-      </c>
-      <c r="H10">
+        <v>95</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>98.3899993896484</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E10" t="n">
+        <v>22.1311511444733</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.19495375522558</v>
+      </c>
+      <c r="H10" t="n">
         <v>10.4274913828344</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>2.62</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>45470</v>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45485</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1630.94</v>
-      </c>
-      <c r="D11">
+        <v>96</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18478.877776</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E11" t="n">
+        <v>18.9976255788459</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.1615148555982</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.6415338967120103</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45485</v>
+      </c>
+      <c r="B12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>1649.82</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>14.0286196499853</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10.3610202484397</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8.2139158364711307</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45485</v>
+      </c>
+      <c r="B13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>107.51000213623</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>14.0286196499853</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.57163751888196</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8.0849810365515502</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45484</v>
+      </c>
+      <c r="B14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>1.34025707</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E14" t="n">
+        <v>13.0848004136224</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9.8908742843961</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7.5706487926186803</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45485</v>
+      </c>
+      <c r="B15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>9351.367494</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10.2961408608194</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8.86011126237019</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7.0585609779296297</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45482</v>
+      </c>
+      <c r="B16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>5062.27</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E16" t="n">
+        <v>8.08498103655155</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6.37076914025385</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6.6759626640876801</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45484</v>
+      </c>
+      <c r="B17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>3676.286177</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6.54870868514921</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="G17" t="n">
+        <v>16.2622315317349</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6.5487086851492098</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45484</v>
+      </c>
+      <c r="B18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>1.83718938</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6.16778118644983</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="G18" t="n">
+        <v>16.6409623765453</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5.9145235035986001</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45485</v>
+      </c>
+      <c r="B19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>99.5199966430664</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5.28380019408186</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5.61199209141845</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.53147769825524</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45485</v>
+      </c>
+      <c r="B20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>3263.51876234143</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4.78170254131676</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="G20" t="n">
+        <v>11.733150721218</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.1650049434697798</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45485</v>
+      </c>
+      <c r="B21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.7951830643242</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5.49628817489687</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.96423528430107397</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45485</v>
+      </c>
+      <c r="B22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>104.089996337891</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-18.3976927066308</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3.55153184843484</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.120066022004939</v>
+      </c>
+      <c r="I22" t="n">
         <v>0.9</v>
       </c>
-      <c r="E11">
-        <v>11.350967495666801</v>
-      </c>
-      <c r="F11">
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="G11">
-        <v>10.4845647858987</v>
-      </c>
-      <c r="H11">
-        <v>9.6415338967120103</v>
-      </c>
-      <c r="I11">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>45471</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="1">
-        <v>97.069999694824205</v>
-      </c>
-      <c r="D12">
-        <v>0.89</v>
-      </c>
-      <c r="E12">
-        <v>11.2186103609413</v>
-      </c>
-      <c r="F12">
-        <v>-0.71</v>
-      </c>
-      <c r="G12">
-        <v>2.0363303500997798</v>
-      </c>
-      <c r="H12">
-        <v>8.2139158364711307</v>
-      </c>
-      <c r="I12">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>45471</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="1">
-        <v>3250.7306934221501</v>
-      </c>
-      <c r="D13">
-        <v>0.79</v>
-      </c>
-      <c r="E13">
-        <v>9.9029481205437797</v>
-      </c>
-      <c r="F13">
-        <v>5.22</v>
-      </c>
-      <c r="G13">
-        <v>11.861866090733001</v>
-      </c>
-      <c r="H13">
-        <v>8.0849810365515502</v>
-      </c>
-      <c r="I13">
-        <v>-7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>45471</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="1">
-        <v>106.779998779297</v>
-      </c>
-      <c r="D14">
-        <v>0.76</v>
-      </c>
-      <c r="E14">
-        <v>9.5110406408293695</v>
-      </c>
-      <c r="F14">
-        <v>0.74</v>
-      </c>
-      <c r="G14">
-        <v>2.2518710310908099</v>
-      </c>
-      <c r="H14">
-        <v>7.5706487926186803</v>
-      </c>
-      <c r="I14">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>45471</v>
-      </c>
-      <c r="B15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="1">
-        <v>99.489997863769503</v>
-      </c>
-      <c r="D15">
-        <v>0.59</v>
-      </c>
-      <c r="E15">
-        <v>7.3143248890742898</v>
-      </c>
-      <c r="F15">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="G15">
-        <v>5.1700995629026201</v>
-      </c>
-      <c r="H15">
-        <v>7.0585609779296297</v>
-      </c>
-      <c r="I15">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>45468</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="1">
-        <v>5019.12</v>
-      </c>
-      <c r="D16">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="E16">
-        <v>6.8033559467648397</v>
-      </c>
-      <c r="F16">
-        <v>-0.01</v>
-      </c>
-      <c r="G16">
-        <v>5.2255092906094802</v>
-      </c>
-      <c r="H16">
-        <v>6.6759626640876801</v>
-      </c>
-      <c r="I16">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>45471</v>
-      </c>
-      <c r="B17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="1">
-        <v>100.709999084473</v>
-      </c>
-      <c r="D17">
-        <v>0.4</v>
-      </c>
-      <c r="E17">
-        <v>4.9070207534805697</v>
-      </c>
-      <c r="F17">
-        <v>2.65</v>
-      </c>
-      <c r="G17">
-        <v>5.4522193059222799</v>
-      </c>
-      <c r="H17">
-        <v>6.5487086851492098</v>
-      </c>
-      <c r="I17">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>45471</v>
-      </c>
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="1">
-        <v>9274.9067020000002</v>
-      </c>
-      <c r="D18">
-        <v>0.39</v>
-      </c>
-      <c r="E18">
-        <v>4.7817025413167604</v>
-      </c>
-      <c r="F18">
-        <v>3.32</v>
-      </c>
-      <c r="G18">
-        <v>8.4391317864746593</v>
-      </c>
-      <c r="H18">
-        <v>5.9145235035986001</v>
-      </c>
-      <c r="I18">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>45470</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" s="1">
-        <v>2163.3704269999998</v>
-      </c>
-      <c r="D19">
-        <v>-0.24</v>
-      </c>
-      <c r="E19">
-        <v>-2.8422864919975299</v>
-      </c>
-      <c r="F19">
-        <v>3.06</v>
-      </c>
-      <c r="G19">
-        <v>9.7501393330649702</v>
-      </c>
-      <c r="H19">
-        <v>4.53147769825524</v>
-      </c>
-      <c r="I19">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>45470</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1.3262792000000001</v>
-      </c>
-      <c r="D20">
-        <v>-0.28000000000000003</v>
-      </c>
-      <c r="E20">
-        <v>-3.3087359150390201</v>
-      </c>
-      <c r="F20">
-        <v>3.31</v>
-      </c>
-      <c r="G20">
-        <v>9.7698021708244198</v>
-      </c>
-      <c r="H20">
-        <v>3.1650049434697798</v>
-      </c>
-      <c r="I20">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>45471</v>
-      </c>
-      <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" s="1">
-        <v>18213.783502999999</v>
-      </c>
-      <c r="D21">
-        <v>-0.28999999999999998</v>
-      </c>
-      <c r="E21">
-        <v>-3.42502707314907</v>
-      </c>
-      <c r="F21">
-        <v>1.51</v>
-      </c>
-      <c r="G21">
-        <v>8.3301007386410202</v>
-      </c>
-      <c r="H21">
-        <v>0.96423528430107397</v>
-      </c>
-      <c r="I21">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <v>45471</v>
-      </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="1">
-        <v>9798.3126709999997</v>
-      </c>
-      <c r="D22">
-        <v>-0.97</v>
-      </c>
-      <c r="E22">
-        <v>-11.038653310901999</v>
-      </c>
-      <c r="F22">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="G22">
-        <v>3.9334380014737902</v>
-      </c>
-      <c r="H22">
-        <v>0.120066022004939</v>
-      </c>
-      <c r="I22">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <v>45471</v>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45485</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" s="1">
-        <v>2047.68994140625</v>
-      </c>
-      <c r="D23">
-        <v>-1.08</v>
-      </c>
-      <c r="E23">
-        <v>-12.217227713764199</v>
-      </c>
-      <c r="F23">
-        <v>1.02</v>
-      </c>
-      <c r="G23">
-        <v>10.1672657079554</v>
-      </c>
-      <c r="H23">
+        <v>108</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>5.4529</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-20.6591562971672</v>
+      </c>
+      <c r="F23" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="G23" t="n">
+        <v>11.3996200126662</v>
+      </c>
+      <c r="H23" t="n">
         <v>-8.1950436713639405</v>
       </c>
-      <c r="I23">
+      <c r="I23" t="n">
         <v>-4.53</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="B24" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="1" t="n">
         <v>10.5</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="B25" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="1" t="n">
         <v>5.5</v>
       </c>
     </row>
@@ -1324,16 +1404,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" customWidth="1"/>
-    <col min="2" max="2" width="117" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="117" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -1344,7 +1424,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1355,7 +1435,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1366,7 +1446,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1377,7 +1457,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -1388,7 +1468,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1399,7 +1479,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -1410,7 +1490,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1421,7 +1501,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1432,7 +1512,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1443,7 +1523,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1454,7 +1534,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1465,7 +1545,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1476,7 +1556,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1487,7 +1567,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1498,7 +1578,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -1509,7 +1589,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1520,7 +1600,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -1531,7 +1611,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -1542,7 +1622,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1553,7 +1633,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -1564,7 +1644,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>42</v>
       </c>

--- a/Dados/fechamento_mes.xlsx
+++ b/Dados/fechamento_mes.xlsx
@@ -1,13 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capribr-my.sharepoint.com/personal/luizlopes_capribr_onmicrosoft_com/Documents/desempenho-ativos/Dados/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_FD14D649DF42C35A21DC1885C46365C5556A476A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="6465" yWindow="1800" windowWidth="19725" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Fechamento" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Glossário" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Fechamento" sheetId="1" r:id="rId1"/>
+    <sheet name="Glossário" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fechamento!$A$1:$D$21</definedName>
@@ -17,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="82">
   <si>
     <t>Dólar</t>
   </si>
@@ -172,15 +179,15 @@
     <t>FFR (upper bound)</t>
   </si>
   <si>
-    <t>Número Índice</t>
-  </si>
-  <si>
     <t>Data</t>
   </si>
   <si>
     <t>Ativo</t>
   </si>
   <si>
+    <t>N�mero �ndice</t>
+  </si>
+  <si>
     <t>Var% no mes</t>
   </si>
   <si>
@@ -193,157 +200,76 @@
     <t>Var% em 12 meses</t>
   </si>
   <si>
+    <t>RUT</t>
+  </si>
+  <si>
+    <t>DJI</t>
+  </si>
+  <si>
+    <t>Ibovespa</t>
+  </si>
+  <si>
+    <t>AGG</t>
+  </si>
+  <si>
+    <t>HG</t>
+  </si>
+  <si>
+    <t>IDA-IPCA Infraestrutura</t>
+  </si>
+  <si>
+    <t>IMA-B</t>
+  </si>
+  <si>
+    <t>HY</t>
+  </si>
+  <si>
     <t>Dólar</t>
   </si>
   <si>
+    <t>TIP</t>
+  </si>
+  <si>
+    <t>SMLL</t>
+  </si>
+  <si>
+    <t>IRF-M</t>
+  </si>
+  <si>
+    <t>IHFA</t>
+  </si>
+  <si>
+    <t>IDA-DI</t>
+  </si>
+  <si>
+    <t>Idex-Infra Geral JGP</t>
+  </si>
+  <si>
+    <t>Idex-CDI Geral JGP</t>
+  </si>
+  <si>
+    <t>SPX</t>
+  </si>
+  <si>
+    <t>CDI</t>
+  </si>
+  <si>
+    <t>IMA-B 5</t>
+  </si>
+  <si>
+    <t>STIP</t>
+  </si>
+  <si>
+    <t>IFIX</t>
+  </si>
+  <si>
+    <t>SGOV</t>
+  </si>
+  <si>
     <t>IXIC</t>
   </si>
   <si>
-    <t>SPX</t>
-  </si>
-  <si>
-    <t>Ibovespa</t>
-  </si>
-  <si>
     <t>DXY</t>
-  </si>
-  <si>
-    <t>DJI</t>
-  </si>
-  <si>
-    <t>Idex-CDI Geral JGP</t>
-  </si>
-  <si>
-    <t>HG</t>
-  </si>
-  <si>
-    <t>IDA-DI</t>
-  </si>
-  <si>
-    <t>HY</t>
-  </si>
-  <si>
-    <t>AGG</t>
-  </si>
-  <si>
-    <t>CDI</t>
-  </si>
-  <si>
-    <t>TIP</t>
-  </si>
-  <si>
-    <t>STIP</t>
-  </si>
-  <si>
-    <t>IHFA</t>
-  </si>
-  <si>
-    <t>SGOV</t>
-  </si>
-  <si>
-    <t>IMA-B 5</t>
-  </si>
-  <si>
-    <t>IDA-IPCA Infraestrutura</t>
-  </si>
-  <si>
-    <t>Idex-Infra Geral JGP</t>
-  </si>
-  <si>
-    <t>IRF-M</t>
-  </si>
-  <si>
-    <t>IMA-B</t>
-  </si>
-  <si>
-    <t>RUT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ativo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N�mero �ndice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Var% no mes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Var% no mes anualizado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Var% no ano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Var% em 12 meses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ibovespa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IXIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DJI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMA-B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDA-IPCA Infraestrutura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRF-M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idex-Infra Geral JGP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMA-B 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHFA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDA-DI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idex-CDI Geral JGP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STIP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SGOV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DXY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dólar</t>
   </si>
 </sst>
 </file>
@@ -351,9 +277,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -389,8 +315,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -694,42 +620,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="12" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="22.85546875" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" customWidth="1"/>
+    <col min="8" max="8" width="22.85546875" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="B1" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="D1" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="E1" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F1" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="G1" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="H1" t="s">
         <v>48</v>
@@ -738,657 +664,703 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>45485</v>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>45504</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>2148.27001953125</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="E2" t="n">
-        <v>77.7471493338375</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="G2" t="n">
-        <v>11.1147324429613</v>
-      </c>
-      <c r="H2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2254.47998046875</v>
+      </c>
+      <c r="D2">
+        <v>10.1</v>
+      </c>
+      <c r="E2">
+        <v>217.28374840078001</v>
+      </c>
+      <c r="F2">
+        <v>11.22</v>
+      </c>
+      <c r="G2">
+        <v>12.545049372485201</v>
+      </c>
+      <c r="H2">
         <v>49.190930936488598</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>4.8099999999999996</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>45485</v>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>45504</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>128896.98</v>
-      </c>
-      <c r="D3" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="E3" t="n">
-        <v>60.6583054281429</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>-3.94</v>
-      </c>
-      <c r="G3" t="n">
-        <v>9.64774771954571</v>
-      </c>
-      <c r="H3" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="C3" s="1">
+        <v>40842.7890625</v>
+      </c>
+      <c r="D3">
+        <v>4.41</v>
+      </c>
+      <c r="E3">
+        <v>67.843740374075594</v>
+      </c>
+      <c r="F3" s="1">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="G3">
+        <v>14.8575012852565</v>
+      </c>
+      <c r="H3" s="1">
         <v>44.246067945403396</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>10.16</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>45485</v>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>45504</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>18398.44921875</v>
-      </c>
-      <c r="D4" t="n">
+        <v>60</v>
+      </c>
+      <c r="C4" s="1">
+        <v>127651.81</v>
+      </c>
+      <c r="D4">
+        <v>3.02</v>
+      </c>
+      <c r="E4">
+        <v>42.908659837256401</v>
+      </c>
+      <c r="F4" s="1">
+        <v>-4.87</v>
+      </c>
+      <c r="G4" s="1">
+        <v>6.2108989890846198</v>
+      </c>
+      <c r="H4">
+        <v>28.022981310051499</v>
+      </c>
+      <c r="I4">
+        <v>5.62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>45504</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="1">
+        <v>99.110000610351605</v>
+      </c>
+      <c r="D5">
+        <v>2.42</v>
+      </c>
+      <c r="E5">
+        <v>33.234672267735398</v>
+      </c>
+      <c r="F5">
+        <v>1.69</v>
+      </c>
+      <c r="G5">
+        <v>5.0863795575054596</v>
+      </c>
+      <c r="H5">
+        <v>23.726113884365802</v>
+      </c>
+      <c r="I5">
+        <v>9.11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>45504</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3316.66</v>
+      </c>
+      <c r="D6">
+        <v>2.36</v>
+      </c>
+      <c r="E6">
+        <v>32.3010608530128</v>
+      </c>
+      <c r="F6">
+        <v>2.4</v>
+      </c>
+      <c r="G6">
+        <v>9.0733895473500201</v>
+      </c>
+      <c r="H6">
+        <v>15.2527113059203</v>
+      </c>
+      <c r="I6">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2202.4934290000001</v>
+      </c>
+      <c r="D7">
+        <v>2.23</v>
+      </c>
+      <c r="E7">
+        <v>30.2987740426804</v>
+      </c>
+      <c r="F7">
+        <v>4.92</v>
+      </c>
+      <c r="G7">
+        <v>9.6061373640336001</v>
+      </c>
+      <c r="H7">
+        <v>14.8433488405669</v>
+      </c>
+      <c r="I7">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>45504</v>
+      </c>
+      <c r="B8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="1">
+        <v>10003.448845000001</v>
+      </c>
+      <c r="D8">
+        <v>2.09</v>
+      </c>
+      <c r="E8">
+        <v>28.173559658490198</v>
+      </c>
+      <c r="F8">
+        <v>0.97</v>
+      </c>
+      <c r="G8">
+        <v>4.6553284152497802</v>
+      </c>
+      <c r="H8">
+        <v>14.8433488405669</v>
+      </c>
+      <c r="I8">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>45504</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1663.94</v>
+      </c>
+      <c r="D9">
+        <v>1.96</v>
+      </c>
+      <c r="E9">
+        <v>26.228645365126201</v>
+      </c>
+      <c r="F9">
+        <v>4.63</v>
+      </c>
+      <c r="G9">
+        <v>11.5862041215959</v>
+      </c>
+      <c r="H9">
+        <v>14.7071911538915</v>
+      </c>
+      <c r="I9">
         <v>3.75</v>
       </c>
-      <c r="E4" t="n">
-        <v>55.5454331372475</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>22.56</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>32.1826434617517</v>
-      </c>
-      <c r="H4" t="n">
-        <v>28.022981310051499</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5.62</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>45485</v>
-      </c>
-      <c r="B5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>5615.35009765625</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="E5" t="n">
-        <v>39.9409492981759</v>
-      </c>
-      <c r="F5" t="n">
-        <v>17.73</v>
-      </c>
-      <c r="G5" t="n">
-        <v>25.562365869402</v>
-      </c>
-      <c r="H5" t="n">
-        <v>23.726113884365802</v>
-      </c>
-      <c r="I5" t="n">
-        <v>9.11</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>45485</v>
-      </c>
-      <c r="B6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>40000.8984375</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E6" t="n">
-        <v>30.6049989887568</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="G6" t="n">
-        <v>16.4596559376826</v>
-      </c>
-      <c r="H6" t="n">
-        <v>15.2527113059203</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.96</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>45485</v>
-      </c>
-      <c r="B7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>10009.728844</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E7" t="n">
-        <v>29.2321623313199</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5.64820829803443</v>
-      </c>
-      <c r="H7" t="n">
-        <v>14.8433488405669</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>45484</v>
-      </c>
-      <c r="B8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>2194.866737</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="E8" t="n">
-        <v>24.8980546006235</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="G8" t="n">
-        <v>10.4870036025003</v>
-      </c>
-      <c r="H8" t="n">
-        <v>14.8433488405669</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>45485</v>
-      </c>
-      <c r="B9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>3295.65</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="E9" t="n">
-        <v>22.7089438137531</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6.94953756287526</v>
-      </c>
-      <c r="H9" t="n">
-        <v>14.7071911538915</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>45485</v>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>45504</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>98.3899993896484</v>
-      </c>
-      <c r="D10" t="n">
+        <v>66</v>
+      </c>
+      <c r="C10" s="1">
+        <v>5.6620999999999997</v>
+      </c>
+      <c r="D10">
+        <v>1.86</v>
+      </c>
+      <c r="E10">
+        <v>24.751007606933602</v>
+      </c>
+      <c r="F10">
+        <v>16.95</v>
+      </c>
+      <c r="G10">
+        <v>19.825196283833801</v>
+      </c>
+      <c r="H10">
+        <v>10.4274913828344</v>
+      </c>
+      <c r="I10">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>45504</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="1">
+        <v>108.18000030517599</v>
+      </c>
+      <c r="D11">
+        <v>1.73</v>
+      </c>
+      <c r="E11">
+        <v>22.853782957617</v>
+      </c>
+      <c r="F11">
+        <v>2.48</v>
+      </c>
+      <c r="G11">
+        <v>4.2073648341670404</v>
+      </c>
+      <c r="H11">
+        <v>9.6415338967120103</v>
+      </c>
+      <c r="I11">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>45504</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2033.32</v>
+      </c>
+      <c r="D12">
+        <v>1.49</v>
+      </c>
+      <c r="E12">
+        <v>19.420539844210801</v>
+      </c>
+      <c r="F12">
+        <v>-13.59</v>
+      </c>
+      <c r="G12">
+        <v>-12.2843042517946</v>
+      </c>
+      <c r="H12">
+        <v>8.2139158364711307</v>
+      </c>
+      <c r="I12">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>45504</v>
+      </c>
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="1">
+        <v>18457.931940999999</v>
+      </c>
+      <c r="D13">
+        <v>1.34</v>
+      </c>
+      <c r="E13">
+        <v>17.319661015484598</v>
+      </c>
+      <c r="F13">
+        <v>2.87</v>
+      </c>
+      <c r="G13">
+        <v>8.54047908384055</v>
+      </c>
+      <c r="H13">
+        <v>8.0849810365515502</v>
+      </c>
+      <c r="I13">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>45502</v>
+      </c>
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="1">
+        <v>5093.95</v>
+      </c>
+      <c r="D14">
+        <v>1.28</v>
+      </c>
+      <c r="E14">
+        <v>16.488837723293798</v>
+      </c>
+      <c r="F14">
+        <v>1.48</v>
+      </c>
+      <c r="G14">
+        <v>5.5130815549141703</v>
+      </c>
+      <c r="H14">
+        <v>7.5706487926186803</v>
+      </c>
+      <c r="I14">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>45504</v>
+      </c>
+      <c r="B15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3702.5455480000001</v>
+      </c>
+      <c r="D15">
+        <v>1.25</v>
+      </c>
+      <c r="E15">
+        <v>16.0754517722998</v>
+      </c>
+      <c r="F15">
+        <v>8.2799999999999994</v>
+      </c>
+      <c r="G15">
+        <v>15.8232911007371</v>
+      </c>
+      <c r="H15">
+        <v>7.0585609779296297</v>
+      </c>
+      <c r="I15">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>45503</v>
+      </c>
+      <c r="B16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1.3431709999999999</v>
+      </c>
+      <c r="D16">
+        <v>1.25</v>
+      </c>
+      <c r="E16">
+        <v>16.0754517722998</v>
+      </c>
+      <c r="F16">
+        <v>4.62</v>
+      </c>
+      <c r="G16">
+        <v>9.0139371792650405</v>
+      </c>
+      <c r="H16">
+        <v>6.6759626640876801</v>
+      </c>
+      <c r="I16">
         <v>1.68</v>
       </c>
-      <c r="E10" t="n">
-        <v>22.1311511444733</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="G10" t="n">
-        <v>4.19495375522558</v>
-      </c>
-      <c r="H10" t="n">
-        <v>10.4274913828344</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.62</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>45485</v>
-      </c>
-      <c r="B11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>18478.877776</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E11" t="n">
-        <v>18.9976255788459</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="G11" t="n">
-        <v>9.1615148555982</v>
-      </c>
-      <c r="H11" t="n">
-        <v>9.6415338967120103</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>45485</v>
-      </c>
-      <c r="B12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>1649.82</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>14.0286196499853</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="G12" t="n">
-        <v>10.3610202484397</v>
-      </c>
-      <c r="H12" t="n">
-        <v>8.2139158364711307</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>45485</v>
-      </c>
-      <c r="B13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>107.51000213623</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>14.0286196499853</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3.57163751888196</v>
-      </c>
-      <c r="H13" t="n">
-        <v>8.0849810365515502</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>45484</v>
-      </c>
-      <c r="B14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>1.34025707</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E14" t="n">
-        <v>13.0848004136224</v>
-      </c>
-      <c r="F14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G14" t="n">
-        <v>9.8908742843961</v>
-      </c>
-      <c r="H14" t="n">
-        <v>7.5706487926186803</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>45485</v>
-      </c>
-      <c r="B15" t="s">
-        <v>100</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>9351.367494</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E15" t="n">
-        <v>10.2961408608194</v>
-      </c>
-      <c r="F15" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="G15" t="n">
-        <v>8.86011126237019</v>
-      </c>
-      <c r="H15" t="n">
-        <v>7.0585609779296297</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>45482</v>
-      </c>
-      <c r="B16" t="s">
-        <v>101</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>5062.27</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E16" t="n">
-        <v>8.08498103655155</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G16" t="n">
-        <v>6.37076914025385</v>
-      </c>
-      <c r="H16" t="n">
-        <v>6.6759626640876801</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45484</v>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>45503</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>3676.286177</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E17" t="n">
-        <v>6.54870868514921</v>
-      </c>
-      <c r="F17" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="G17" t="n">
-        <v>16.2622315317349</v>
-      </c>
-      <c r="H17" t="n">
+        <v>73</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1.84969614</v>
+      </c>
+      <c r="D17">
+        <v>1.18</v>
+      </c>
+      <c r="E17">
+        <v>15.116108770013099</v>
+      </c>
+      <c r="F17">
+        <v>8.5</v>
+      </c>
+      <c r="G17">
+        <v>15.935958139265701</v>
+      </c>
+      <c r="H17">
         <v>6.5487086851492098</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>3.68</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45484</v>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>45504</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>1.83718938</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E18" t="n">
-        <v>6.16778118644983</v>
-      </c>
-      <c r="F18" t="n">
-        <v>7.77</v>
-      </c>
-      <c r="G18" t="n">
-        <v>16.6409623765453</v>
-      </c>
-      <c r="H18" t="n">
+        <v>74</v>
+      </c>
+      <c r="C18" s="1">
+        <v>5522.2998046875</v>
+      </c>
+      <c r="D18">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="E18">
+        <v>14.4353196047725</v>
+      </c>
+      <c r="F18">
+        <v>15.78</v>
+      </c>
+      <c r="G18">
+        <v>20.3388099197823</v>
+      </c>
+      <c r="H18">
         <v>5.9145235035986001</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>3.85</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45485</v>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>45504</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>99.5199966430664</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E19" t="n">
-        <v>5.28380019408186</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5.61199209141845</v>
-      </c>
-      <c r="H19" t="n">
+        <v>75</v>
+      </c>
+      <c r="C19" s="1">
+        <v>3280.21849055861</v>
+      </c>
+      <c r="D19">
+        <v>0.91</v>
+      </c>
+      <c r="E19">
+        <v>11.483469003274401</v>
+      </c>
+      <c r="F19">
+        <v>6.18</v>
+      </c>
+      <c r="G19">
+        <v>11.5660421369468</v>
+      </c>
+      <c r="H19">
         <v>4.53147769825524</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>3.18</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>45485</v>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>45504</v>
       </c>
       <c r="B20" t="s">
-        <v>105</v>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>3263.51876234143</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E20" t="n">
-        <v>4.78170254131676</v>
-      </c>
-      <c r="F20" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="G20" t="n">
-        <v>11.733150721218</v>
-      </c>
-      <c r="H20" t="n">
+        <v>76</v>
+      </c>
+      <c r="C20" s="1">
+        <v>9359.6766740000003</v>
+      </c>
+      <c r="D20">
+        <v>0.91</v>
+      </c>
+      <c r="E20">
+        <v>11.483469003274401</v>
+      </c>
+      <c r="F20">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="G20">
+        <v>8.2915840971507393</v>
+      </c>
+      <c r="H20">
         <v>3.1650049434697798</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>3.2</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>45485</v>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>45504</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>100.5</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2.7951830643242</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="G21" t="n">
-        <v>5.49628817489687</v>
-      </c>
-      <c r="H21" t="n">
+        <v>77</v>
+      </c>
+      <c r="C21" s="1">
+        <v>99.940002441406193</v>
+      </c>
+      <c r="D21">
+        <v>0.86</v>
+      </c>
+      <c r="E21">
+        <v>10.8224037644802</v>
+      </c>
+      <c r="F21">
+        <v>3.18</v>
+      </c>
+      <c r="G21">
+        <v>5.7314858819519099</v>
+      </c>
+      <c r="H21">
         <v>0.96423528430107397</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>0.18</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>45485</v>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>45504</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>104.089996337891</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-18.3976927066308</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="G22" t="n">
-        <v>3.55153184843484</v>
-      </c>
-      <c r="H22" t="n">
+        <v>78</v>
+      </c>
+      <c r="C22" s="1">
+        <v>3364.78</v>
+      </c>
+      <c r="D22">
+        <v>0.52</v>
+      </c>
+      <c r="E22">
+        <v>6.4215938714558902</v>
+      </c>
+      <c r="F22">
+        <v>1.61</v>
+      </c>
+      <c r="G22">
+        <v>5.7691159135559298</v>
+      </c>
+      <c r="H22">
         <v>0.120066022004939</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>0.9</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>45485</v>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>45504</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>5.4529</v>
-      </c>
-      <c r="D23" t="n">
-        <v>-1.91</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-20.6591562971672</v>
-      </c>
-      <c r="F23" t="n">
-        <v>12.63</v>
-      </c>
-      <c r="G23" t="n">
-        <v>11.3996200126662</v>
-      </c>
-      <c r="H23" t="n">
+        <v>79</v>
+      </c>
+      <c r="C23" s="1">
+        <v>100.720001220703</v>
+      </c>
+      <c r="D23">
+        <v>0.45</v>
+      </c>
+      <c r="E23">
+        <v>5.5356751950101897</v>
+      </c>
+      <c r="F23">
+        <v>3.11</v>
+      </c>
+      <c r="G23">
+        <v>5.4540153425310303</v>
+      </c>
+      <c r="H23">
         <v>-8.1950436713639405</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>-4.53</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>45504</v>
+      </c>
       <c r="B24" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="1">
+        <v>17599.400390625</v>
+      </c>
+      <c r="D24">
+        <v>-0.75</v>
+      </c>
+      <c r="E24">
+        <v>-8.6378764920193394</v>
+      </c>
+      <c r="F24">
+        <v>17.239999999999998</v>
+      </c>
+      <c r="G24">
+        <v>22.677934128614201</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>45504</v>
+      </c>
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="1">
+        <v>104.09999847412099</v>
+      </c>
+      <c r="D25">
+        <v>-1.67</v>
+      </c>
+      <c r="E25">
+        <v>-18.298040992719901</v>
+      </c>
+      <c r="F25">
+        <v>2.73</v>
+      </c>
+      <c r="G25">
+        <v>2.1990946891293999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C26">
         <v>10.5</v>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" t="s">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C27" s="1">
         <v>5.5</v>
       </c>
     </row>
@@ -1404,16 +1376,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="117" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="117" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -1424,7 +1396,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1435,7 +1407,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1446,7 +1418,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1457,7 +1429,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -1468,7 +1440,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1479,7 +1451,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -1490,7 +1462,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1501,7 +1473,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1512,7 +1484,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1523,7 +1495,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1534,7 +1506,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1545,7 +1517,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1556,7 +1528,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1567,7 +1539,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1578,7 +1550,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -1589,7 +1561,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1600,7 +1572,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -1611,7 +1583,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -1622,7 +1594,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1633,7 +1605,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -1644,7 +1616,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>42</v>
       </c>

--- a/Dados/fechamento_mes.xlsx
+++ b/Dados/fechamento_mes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capribr-my.sharepoint.com/personal/luizlopes_capribr_onmicrosoft_com/Documents/desempenho-ativos/Dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_FD14D649DF42C35A21DC1885C46365C5556A476A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_FC14D649DF42CBAA21C7C02184626D552DA86506" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6465" yWindow="1800" windowWidth="19725" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6120" yWindow="1455" windowWidth="19725" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fechamento" sheetId="1" r:id="rId1"/>
@@ -200,76 +200,76 @@
     <t>Var% em 12 meses</t>
   </si>
   <si>
+    <t>Ibovespa</t>
+  </si>
+  <si>
+    <t>SMLL</t>
+  </si>
+  <si>
+    <t>SPX</t>
+  </si>
+  <si>
+    <t>HG</t>
+  </si>
+  <si>
+    <t>DJI</t>
+  </si>
+  <si>
+    <t>HY</t>
+  </si>
+  <si>
+    <t>Idex-Infra Geral JGP</t>
+  </si>
+  <si>
+    <t>IDA-IPCA Infraestrutura</t>
+  </si>
+  <si>
+    <t>AGG</t>
+  </si>
+  <si>
+    <t>IHFA</t>
+  </si>
+  <si>
+    <t>Idex-CDI Geral JGP</t>
+  </si>
+  <si>
+    <t>IDA-DI</t>
+  </si>
+  <si>
+    <t>CDI</t>
+  </si>
+  <si>
+    <t>IFIX</t>
+  </si>
+  <si>
+    <t>TIP</t>
+  </si>
+  <si>
+    <t>IRF-M</t>
+  </si>
+  <si>
+    <t>IXIC</t>
+  </si>
+  <si>
+    <t>STIP</t>
+  </si>
+  <si>
+    <t>IMA-B 5</t>
+  </si>
+  <si>
+    <t>IMA-B</t>
+  </si>
+  <si>
+    <t>SGOV</t>
+  </si>
+  <si>
+    <t>DXY</t>
+  </si>
+  <si>
+    <t>Dólar</t>
+  </si>
+  <si>
     <t>RUT</t>
-  </si>
-  <si>
-    <t>DJI</t>
-  </si>
-  <si>
-    <t>Ibovespa</t>
-  </si>
-  <si>
-    <t>AGG</t>
-  </si>
-  <si>
-    <t>HG</t>
-  </si>
-  <si>
-    <t>IDA-IPCA Infraestrutura</t>
-  </si>
-  <si>
-    <t>IMA-B</t>
-  </si>
-  <si>
-    <t>HY</t>
-  </si>
-  <si>
-    <t>Dólar</t>
-  </si>
-  <si>
-    <t>TIP</t>
-  </si>
-  <si>
-    <t>SMLL</t>
-  </si>
-  <si>
-    <t>IRF-M</t>
-  </si>
-  <si>
-    <t>IHFA</t>
-  </si>
-  <si>
-    <t>IDA-DI</t>
-  </si>
-  <si>
-    <t>Idex-Infra Geral JGP</t>
-  </si>
-  <si>
-    <t>Idex-CDI Geral JGP</t>
-  </si>
-  <si>
-    <t>SPX</t>
-  </si>
-  <si>
-    <t>CDI</t>
-  </si>
-  <si>
-    <t>IMA-B 5</t>
-  </si>
-  <si>
-    <t>STIP</t>
-  </si>
-  <si>
-    <t>IFIX</t>
-  </si>
-  <si>
-    <t>SGOV</t>
-  </si>
-  <si>
-    <t>IXIC</t>
-  </si>
-  <si>
-    <t>DXY</t>
   </si>
 </sst>
 </file>
@@ -291,6 +291,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -666,25 +667,25 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>45504</v>
+        <v>45534</v>
       </c>
       <c r="B2" t="s">
         <v>58</v>
       </c>
       <c r="C2" s="1">
-        <v>2254.47998046875</v>
+        <v>136004.01</v>
       </c>
       <c r="D2">
-        <v>10.1</v>
+        <v>6.54</v>
       </c>
       <c r="E2">
-        <v>217.28374840078001</v>
+        <v>113.87120156771999</v>
       </c>
       <c r="F2">
-        <v>11.22</v>
+        <v>1.36</v>
       </c>
       <c r="G2">
-        <v>12.545049372485201</v>
+        <v>14.864749478499901</v>
       </c>
       <c r="H2">
         <v>49.190930936488598</v>
@@ -695,25 +696,25 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>45504</v>
+        <v>45534</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
       </c>
       <c r="C3" s="1">
-        <v>40842.7890625</v>
+        <v>2124.9899999999998</v>
       </c>
       <c r="D3">
-        <v>4.41</v>
+        <v>4.51</v>
       </c>
       <c r="E3">
-        <v>67.843740374075594</v>
+        <v>69.782988170954795</v>
       </c>
       <c r="F3" s="1">
-        <v>8.3699999999999992</v>
+        <v>-9.69</v>
       </c>
       <c r="G3">
-        <v>14.8575012852565</v>
+        <v>-5.2633690733598897</v>
       </c>
       <c r="H3" s="1">
         <v>44.246067945403396</v>
@@ -724,25 +725,25 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>45504</v>
+        <v>45534</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="1">
-        <v>127651.81</v>
+        <v>5648.39990234375</v>
       </c>
       <c r="D4">
-        <v>3.02</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="E4">
-        <v>42.908659837256401</v>
+        <v>31.065573523050599</v>
       </c>
       <c r="F4" s="1">
-        <v>-4.87</v>
+        <v>18.420000000000002</v>
       </c>
       <c r="G4" s="1">
-        <v>6.2108989890846198</v>
+        <v>25.106586806142001</v>
       </c>
       <c r="H4">
         <v>28.022981310051499</v>
@@ -753,25 +754,25 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>45504</v>
+        <v>45533</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
       </c>
       <c r="C5" s="1">
-        <v>99.110000610351605</v>
+        <v>3377.05</v>
       </c>
       <c r="D5">
-        <v>2.42</v>
+        <v>1.82</v>
       </c>
       <c r="E5">
-        <v>33.234672267735398</v>
+        <v>24.164405198757599</v>
       </c>
       <c r="F5">
-        <v>1.69</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="G5">
-        <v>5.0863795575054596</v>
+        <v>10.644592681904101</v>
       </c>
       <c r="H5">
         <v>23.726113884365802</v>
@@ -782,25 +783,25 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>45504</v>
+        <v>45534</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
       </c>
       <c r="C6" s="1">
-        <v>3316.66</v>
+        <v>41563.078125</v>
       </c>
       <c r="D6">
-        <v>2.36</v>
+        <v>1.76</v>
       </c>
       <c r="E6">
-        <v>32.3010608530128</v>
+        <v>23.2892411958175</v>
       </c>
       <c r="F6">
-        <v>2.4</v>
+        <v>10.28</v>
       </c>
       <c r="G6">
-        <v>9.0733895473500201</v>
+        <v>19.1252343706003</v>
       </c>
       <c r="H6">
         <v>15.2527113059203</v>
@@ -811,25 +812,25 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>45504</v>
+        <v>45533</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="1">
-        <v>2202.4934290000001</v>
+        <v>1690.3</v>
       </c>
       <c r="D7">
-        <v>2.23</v>
+        <v>1.58</v>
       </c>
       <c r="E7">
-        <v>30.2987740426804</v>
+        <v>20.697563152516398</v>
       </c>
       <c r="F7">
-        <v>4.92</v>
+        <v>6.29</v>
       </c>
       <c r="G7">
-        <v>9.6061373640336001</v>
+        <v>12.631852498450799</v>
       </c>
       <c r="H7">
         <v>14.8433488405669</v>
@@ -840,25 +841,25 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>45504</v>
+        <v>45533</v>
       </c>
       <c r="B8" t="s">
         <v>64</v>
       </c>
       <c r="C8" s="1">
-        <v>10003.448845000001</v>
+        <v>1.36843922</v>
       </c>
       <c r="D8">
-        <v>2.09</v>
+        <v>1.54</v>
       </c>
       <c r="E8">
-        <v>28.173559658490198</v>
+        <v>20.128459778538598</v>
       </c>
       <c r="F8">
-        <v>0.97</v>
+        <v>6.59</v>
       </c>
       <c r="G8">
-        <v>4.6553284152497802</v>
+        <v>9.6274232461797293</v>
       </c>
       <c r="H8">
         <v>14.8433488405669</v>
@@ -869,25 +870,25 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>45504</v>
+        <v>45533</v>
       </c>
       <c r="B9" t="s">
         <v>65</v>
       </c>
       <c r="C9" s="1">
-        <v>1663.94</v>
+        <v>2235.4551809999998</v>
       </c>
       <c r="D9">
-        <v>1.96</v>
+        <v>1.5</v>
       </c>
       <c r="E9">
-        <v>26.228645365126201</v>
+        <v>19.561817146153398</v>
       </c>
       <c r="F9">
-        <v>4.63</v>
+        <v>6.49</v>
       </c>
       <c r="G9">
-        <v>11.5862041215959</v>
+        <v>9.83028854045698</v>
       </c>
       <c r="H9">
         <v>14.7071911538915</v>
@@ -898,25 +899,25 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>45504</v>
+        <v>45534</v>
       </c>
       <c r="B10" t="s">
         <v>66</v>
       </c>
       <c r="C10" s="1">
-        <v>5.6620999999999997</v>
+        <v>100.25</v>
       </c>
       <c r="D10">
-        <v>1.86</v>
+        <v>1.46</v>
       </c>
       <c r="E10">
-        <v>24.751007606933602</v>
+        <v>18.997625578845899</v>
       </c>
       <c r="F10">
-        <v>16.95</v>
+        <v>3.18</v>
       </c>
       <c r="G10">
-        <v>19.825196283833801</v>
+        <v>7.4549726586127001</v>
       </c>
       <c r="H10">
         <v>10.4274913828344</v>
@@ -927,25 +928,25 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>45504</v>
+        <v>45531</v>
       </c>
       <c r="B11" t="s">
         <v>67</v>
       </c>
       <c r="C11" s="1">
-        <v>108.18000030517599</v>
+        <v>5162.78</v>
       </c>
       <c r="D11">
-        <v>1.73</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="E11">
-        <v>22.853782957617</v>
+        <v>14.2996054499739</v>
       </c>
       <c r="F11">
-        <v>2.48</v>
+        <v>2.85</v>
       </c>
       <c r="G11">
-        <v>4.2073648341670404</v>
+        <v>6.7899191646738402</v>
       </c>
       <c r="H11">
         <v>9.6415338967120103</v>
@@ -956,25 +957,25 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>45504</v>
+        <v>45533</v>
       </c>
       <c r="B12" t="s">
         <v>68</v>
       </c>
       <c r="C12" s="1">
-        <v>2033.32</v>
+        <v>1.87373203</v>
       </c>
       <c r="D12">
-        <v>1.49</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="E12">
-        <v>19.420539844210801</v>
+        <v>14.2996054499739</v>
       </c>
       <c r="F12">
-        <v>-13.59</v>
+        <v>9.91</v>
       </c>
       <c r="G12">
-        <v>-12.2843042517946</v>
+        <v>15.469788262643799</v>
       </c>
       <c r="H12">
         <v>8.2139158364711307</v>
@@ -985,25 +986,25 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>45504</v>
+        <v>45533</v>
       </c>
       <c r="B13" t="s">
         <v>69</v>
       </c>
       <c r="C13" s="1">
-        <v>18457.931940999999</v>
+        <v>3742.6224510000002</v>
       </c>
       <c r="D13">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="E13">
-        <v>17.319661015484598</v>
+        <v>13.7582228911072</v>
       </c>
       <c r="F13">
-        <v>2.87</v>
+        <v>9.4600000000000009</v>
       </c>
       <c r="G13">
-        <v>8.54047908384055</v>
+        <v>15.034867532011001</v>
       </c>
       <c r="H13">
         <v>8.0849810365515502</v>
@@ -1014,25 +1015,25 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>45502</v>
+        <v>45534</v>
       </c>
       <c r="B14" t="s">
         <v>70</v>
       </c>
       <c r="C14" s="1">
-        <v>5093.95</v>
+        <v>3308.6744723195602</v>
       </c>
       <c r="D14">
-        <v>1.28</v>
+        <v>0.87</v>
       </c>
       <c r="E14">
-        <v>16.488837723293798</v>
+        <v>10.954328638178</v>
       </c>
       <c r="F14">
-        <v>1.48</v>
+        <v>7.1</v>
       </c>
       <c r="G14">
-        <v>5.5130815549141703</v>
+        <v>11.3188655493522</v>
       </c>
       <c r="H14">
         <v>7.5706487926186803</v>
@@ -1043,25 +1044,25 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>45504</v>
+        <v>45534</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
       </c>
       <c r="C15" s="1">
-        <v>3702.5455480000001</v>
+        <v>3393.55</v>
       </c>
       <c r="D15">
-        <v>1.25</v>
+        <v>0.86</v>
       </c>
       <c r="E15">
-        <v>16.0754517722998</v>
+        <v>10.8224037644802</v>
       </c>
       <c r="F15">
-        <v>8.2799999999999994</v>
+        <v>2.48</v>
       </c>
       <c r="G15">
-        <v>15.8232911007371</v>
+        <v>6.2999032085276196</v>
       </c>
       <c r="H15">
         <v>7.0585609779296297</v>
@@ -1072,25 +1073,25 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>45503</v>
+        <v>45534</v>
       </c>
       <c r="B16" t="s">
         <v>72</v>
       </c>
       <c r="C16" s="1">
-        <v>1.3431709999999999</v>
+        <v>108.870002746582</v>
       </c>
       <c r="D16">
-        <v>1.25</v>
+        <v>0.8</v>
       </c>
       <c r="E16">
-        <v>16.0754517722998</v>
+        <v>10.0338693716146</v>
       </c>
       <c r="F16">
-        <v>4.62</v>
+        <v>3.3</v>
       </c>
       <c r="G16">
-        <v>9.0139371792650405</v>
+        <v>6.1206716018768104</v>
       </c>
       <c r="H16">
         <v>6.6759626640876801</v>
@@ -1101,25 +1102,25 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>45503</v>
+        <v>45534</v>
       </c>
       <c r="B17" t="s">
         <v>73</v>
       </c>
       <c r="C17" s="1">
-        <v>1.84969614</v>
+        <v>18579.102225999999</v>
       </c>
       <c r="D17">
-        <v>1.18</v>
+        <v>0.66</v>
       </c>
       <c r="E17">
-        <v>15.116108770013099</v>
+        <v>8.2139158364711307</v>
       </c>
       <c r="F17">
-        <v>8.5</v>
+        <v>3.54</v>
       </c>
       <c r="G17">
-        <v>15.935958139265701</v>
+        <v>8.0437269984020308</v>
       </c>
       <c r="H17">
         <v>6.5487086851492098</v>
@@ -1130,25 +1131,25 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>45504</v>
+        <v>45534</v>
       </c>
       <c r="B18" t="s">
         <v>74</v>
       </c>
       <c r="C18" s="1">
-        <v>5522.2998046875</v>
+        <v>17713.619140625</v>
       </c>
       <c r="D18">
-        <v>1.1299999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="E18">
-        <v>14.4353196047725</v>
+        <v>8.0849810365515502</v>
       </c>
       <c r="F18">
-        <v>15.78</v>
+        <v>18</v>
       </c>
       <c r="G18">
-        <v>20.3388099197823</v>
+        <v>26.3515799532356</v>
       </c>
       <c r="H18">
         <v>5.9145235035986001</v>
@@ -1159,25 +1160,25 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>45504</v>
+        <v>45534</v>
       </c>
       <c r="B19" t="s">
         <v>75</v>
       </c>
       <c r="C19" s="1">
-        <v>3280.21849055861</v>
+        <v>100.370002746582</v>
       </c>
       <c r="D19">
-        <v>0.91</v>
+        <v>0.62</v>
       </c>
       <c r="E19">
-        <v>11.483469003274401</v>
+        <v>7.6990210897167204</v>
       </c>
       <c r="F19">
-        <v>6.18</v>
+        <v>3.82</v>
       </c>
       <c r="G19">
-        <v>11.5660421369468</v>
+        <v>6.3450304783017897</v>
       </c>
       <c r="H19">
         <v>4.53147769825524</v>
@@ -1188,25 +1189,25 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>45504</v>
+        <v>45534</v>
       </c>
       <c r="B20" t="s">
         <v>76</v>
       </c>
       <c r="C20" s="1">
-        <v>9359.6766740000003</v>
+        <v>9414.8941670000004</v>
       </c>
       <c r="D20">
-        <v>0.91</v>
+        <v>0.59</v>
       </c>
       <c r="E20">
-        <v>11.483469003274401</v>
+        <v>7.3143248890742898</v>
       </c>
       <c r="F20">
-        <v>4.2699999999999996</v>
+        <v>4.88</v>
       </c>
       <c r="G20">
-        <v>8.2915840971507393</v>
+        <v>7.8011067183189304</v>
       </c>
       <c r="H20">
         <v>3.1650049434697798</v>
@@ -1217,25 +1218,25 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>45504</v>
+        <v>45534</v>
       </c>
       <c r="B21" t="s">
         <v>77</v>
       </c>
       <c r="C21" s="1">
-        <v>99.940002441406193</v>
+        <v>10055.168258</v>
       </c>
       <c r="D21">
-        <v>0.86</v>
+        <v>0.52</v>
       </c>
       <c r="E21">
-        <v>10.8224037644802</v>
+        <v>6.4215938714558902</v>
       </c>
       <c r="F21">
-        <v>3.18</v>
+        <v>1.49</v>
       </c>
       <c r="G21">
-        <v>5.7314858819519099</v>
+        <v>4.4492816525188497</v>
       </c>
       <c r="H21">
         <v>0.96423528430107397</v>
@@ -1246,25 +1247,25 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>45504</v>
+        <v>45534</v>
       </c>
       <c r="B22" t="s">
         <v>78</v>
       </c>
       <c r="C22" s="1">
-        <v>3364.78</v>
+        <v>100.73999786377</v>
       </c>
       <c r="D22">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="E22">
-        <v>6.4215938714558902</v>
+        <v>5.7881024430621197</v>
       </c>
       <c r="F22">
-        <v>1.61</v>
+        <v>3.59</v>
       </c>
       <c r="G22">
-        <v>5.7691159135559298</v>
+        <v>5.48608289499923</v>
       </c>
       <c r="H22">
         <v>0.120066022004939</v>
@@ -1275,25 +1276,25 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>45504</v>
+        <v>45537</v>
       </c>
       <c r="B23" t="s">
         <v>79</v>
       </c>
       <c r="C23" s="1">
-        <v>100.720001220703</v>
+        <v>101.709999084473</v>
       </c>
       <c r="D23">
-        <v>0.45</v>
+        <v>0.01</v>
       </c>
       <c r="E23">
-        <v>5.5356751950101897</v>
+        <v>0.120066022004939</v>
       </c>
       <c r="F23">
-        <v>3.11</v>
+        <v>0.38</v>
       </c>
       <c r="G23">
-        <v>5.4540153425310303</v>
+        <v>-1.8432769846383501</v>
       </c>
       <c r="H23">
         <v>-8.1950436713639405</v>
@@ -1304,48 +1305,48 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>45504</v>
+        <v>45534</v>
       </c>
       <c r="B24" t="s">
         <v>80</v>
       </c>
       <c r="C24" s="1">
-        <v>17599.400390625</v>
+        <v>5.6562000000000001</v>
       </c>
       <c r="D24">
-        <v>-0.75</v>
+        <v>-0.1</v>
       </c>
       <c r="E24">
-        <v>-8.6378764920193394</v>
+        <v>-1.1934219505791099</v>
       </c>
       <c r="F24">
-        <v>17.239999999999998</v>
+        <v>16.829999999999998</v>
       </c>
       <c r="G24">
-        <v>22.677934128614201</v>
+        <v>16.129429639058898</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>45504</v>
+        <v>45534</v>
       </c>
       <c r="B25" t="s">
         <v>81</v>
       </c>
       <c r="C25" s="1">
-        <v>104.09999847412099</v>
+        <v>2217.6298828125</v>
       </c>
       <c r="D25">
-        <v>-1.67</v>
+        <v>-1.63</v>
       </c>
       <c r="E25">
-        <v>-18.298040992719901</v>
+        <v>-17.898317592139101</v>
       </c>
       <c r="F25">
-        <v>2.73</v>
+        <v>9.4</v>
       </c>
       <c r="G25">
-        <v>2.1990946891293999</v>
+        <v>16.520506319761001</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">

--- a/Dados/fechamento_mes.xlsx
+++ b/Dados/fechamento_mes.xlsx
@@ -1,20 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capribr-my.sharepoint.com/personal/luizlopes_capribr_onmicrosoft_com/Documents/desempenho-ativos/Dados/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_FC14D649DF42CBAA21C7C02184626D552DA86506" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6120" yWindow="1455" windowWidth="19725" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Fechamento" sheetId="1" r:id="rId1"/>
-    <sheet name="Glossário" sheetId="2" r:id="rId2"/>
+    <sheet name="Fechamento" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Glossário" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fechamento!$A$1:$D$21</definedName>
@@ -24,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <si>
     <t>Dólar</t>
   </si>
@@ -200,76 +193,208 @@
     <t>Var% em 12 meses</t>
   </si>
   <si>
+    <t>IXIC</t>
+  </si>
+  <si>
+    <t>SPX</t>
+  </si>
+  <si>
+    <t>HG</t>
+  </si>
+  <si>
+    <t>DJI</t>
+  </si>
+  <si>
+    <t>HY</t>
+  </si>
+  <si>
+    <t>TIP</t>
+  </si>
+  <si>
+    <t>AGG</t>
+  </si>
+  <si>
+    <t>STIP</t>
+  </si>
+  <si>
+    <t>Idex-CDI Geral JGP</t>
+  </si>
+  <si>
+    <t>IHFA</t>
+  </si>
+  <si>
+    <t>IDA-DI</t>
+  </si>
+  <si>
+    <t>CDI</t>
+  </si>
+  <si>
+    <t>RUT</t>
+  </si>
+  <si>
+    <t>Idex-Infra Geral JGP</t>
+  </si>
+  <si>
+    <t>SGOV</t>
+  </si>
+  <si>
+    <t>IMA-B 5</t>
+  </si>
+  <si>
+    <t>IRF-M</t>
+  </si>
+  <si>
+    <t>IDA-IPCA Infraestrutura</t>
+  </si>
+  <si>
+    <t>IMA-B</t>
+  </si>
+  <si>
+    <t>DXY</t>
+  </si>
+  <si>
+    <t>IFIX</t>
+  </si>
+  <si>
     <t>Ibovespa</t>
   </si>
   <si>
+    <t>Dólar</t>
+  </si>
+  <si>
     <t>SMLL</t>
   </si>
   <si>
-    <t>SPX</t>
-  </si>
-  <si>
-    <t>HG</t>
-  </si>
-  <si>
-    <t>DJI</t>
-  </si>
-  <si>
-    <t>HY</t>
-  </si>
-  <si>
-    <t>Idex-Infra Geral JGP</t>
-  </si>
-  <si>
-    <t>IDA-IPCA Infraestrutura</t>
-  </si>
-  <si>
-    <t>AGG</t>
-  </si>
-  <si>
-    <t>IHFA</t>
-  </si>
-  <si>
-    <t>Idex-CDI Geral JGP</t>
-  </si>
-  <si>
-    <t>IDA-DI</t>
-  </si>
-  <si>
-    <t>CDI</t>
-  </si>
-  <si>
-    <t>IFIX</t>
-  </si>
-  <si>
-    <t>TIP</t>
-  </si>
-  <si>
-    <t>IRF-M</t>
-  </si>
-  <si>
-    <t>IXIC</t>
-  </si>
-  <si>
-    <t>STIP</t>
-  </si>
-  <si>
-    <t>IMA-B 5</t>
-  </si>
-  <si>
-    <t>IMA-B</t>
-  </si>
-  <si>
-    <t>SGOV</t>
-  </si>
-  <si>
-    <t>DXY</t>
-  </si>
-  <si>
-    <t>Dólar</t>
-  </si>
-  <si>
-    <t>RUT</t>
+    <t xml:space="preserve">Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N�mero �ndice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Var% no mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Var% no mes anualizado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Var% no ano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Var% em 12 meses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IXIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DJI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDA-DI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idex-CDI Geral JGP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IHFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idex-Infra Geral JGP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGOV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMA-B 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRF-M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDA-IPCA Infraestrutura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMA-B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DXY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IFIX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ibovespa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dólar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMLL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dxy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ixic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spxew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sgov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPXEW</t>
   </si>
 </sst>
 </file>
@@ -277,9 +402,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -291,7 +416,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -316,8 +440,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -621,42 +745,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="8" width="22.85546875" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="22.85546875" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="12" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D1" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E1" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G1" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="H1" t="s">
         <v>48</v>
@@ -665,704 +789,719 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>45534</v>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>45576</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="1">
-        <v>136004.01</v>
-      </c>
-      <c r="D2">
-        <v>6.54</v>
-      </c>
-      <c r="E2">
-        <v>113.87120156771999</v>
-      </c>
-      <c r="F2">
-        <v>1.36</v>
-      </c>
-      <c r="G2">
-        <v>14.864749478499901</v>
-      </c>
-      <c r="H2">
+        <v>111</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>5.6263</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="E2" t="n">
+        <v>47.1262359655801</v>
+      </c>
+      <c r="F2" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="G2" t="n">
+        <v>11.420706590621</v>
+      </c>
+      <c r="H2" t="n">
         <v>49.190930936488598</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>4.8099999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>45534</v>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45576</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="1">
-        <v>2124.9899999999998</v>
-      </c>
-      <c r="D3">
-        <v>4.51</v>
-      </c>
-      <c r="E3">
-        <v>69.782988170954795</v>
-      </c>
-      <c r="F3" s="1">
-        <v>-9.69</v>
-      </c>
-      <c r="G3">
-        <v>-5.2633690733598897</v>
-      </c>
-      <c r="H3" s="1">
+        <v>108</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>102.889999389648</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E3" t="n">
+        <v>28.1735596584902</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-2.76885306522938</v>
+      </c>
+      <c r="H3" s="1" t="n">
         <v>44.246067945403396</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>10.16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>45534</v>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45576</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="1">
-        <v>5648.39990234375</v>
-      </c>
-      <c r="D4">
-        <v>2.2799999999999998</v>
-      </c>
-      <c r="E4">
-        <v>31.065573523050599</v>
-      </c>
-      <c r="F4" s="1">
-        <v>18.420000000000002</v>
-      </c>
-      <c r="G4" s="1">
-        <v>25.106586806142001</v>
-      </c>
-      <c r="H4">
+        <v>92</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>42863.859375</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E4" t="n">
+        <v>16.2130974325867</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>26.7978784954598</v>
+      </c>
+      <c r="H4" t="n">
         <v>28.022981310051499</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>5.62</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>45533</v>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45576</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="1">
-        <v>3377.05</v>
-      </c>
-      <c r="D5">
-        <v>1.82</v>
-      </c>
-      <c r="E5">
-        <v>24.164405198757599</v>
-      </c>
-      <c r="F5">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="G5">
-        <v>10.644592681904101</v>
-      </c>
-      <c r="H5">
+        <v>90</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>5815.02978515625</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11.4834690032744</v>
+      </c>
+      <c r="F5" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="G5" t="n">
+        <v>32.8557448833632</v>
+      </c>
+      <c r="H5" t="n">
         <v>23.726113884365802</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>9.11</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>45534</v>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45576</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="1">
-        <v>41563.078125</v>
-      </c>
-      <c r="D6">
-        <v>1.76</v>
-      </c>
-      <c r="E6">
-        <v>23.2892411958175</v>
-      </c>
-      <c r="F6">
-        <v>10.28</v>
-      </c>
-      <c r="G6">
-        <v>19.1252343706003</v>
-      </c>
-      <c r="H6">
+        <v>89</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>18342.939453125</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10.6906226923436</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="G6" t="n">
+        <v>34.285282471965</v>
+      </c>
+      <c r="H6" t="n">
         <v>15.2527113059203</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>3.96</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>45533</v>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45576</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1690.3</v>
-      </c>
-      <c r="D7">
-        <v>1.58</v>
-      </c>
-      <c r="E7">
-        <v>20.697563152516398</v>
-      </c>
-      <c r="F7">
-        <v>6.29</v>
-      </c>
-      <c r="G7">
-        <v>12.631852498450799</v>
-      </c>
-      <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>3348.3571669944</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.40657079419022</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8.38</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11.0365385950729</v>
+      </c>
+      <c r="H7" t="n">
         <v>14.8433488405669</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>-0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>45533</v>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45576</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1.36843922</v>
-      </c>
-      <c r="D8">
-        <v>1.54</v>
-      </c>
-      <c r="E8">
-        <v>20.128459778538598</v>
-      </c>
-      <c r="F8">
-        <v>6.59</v>
-      </c>
-      <c r="G8">
-        <v>9.6274232461797293</v>
-      </c>
-      <c r="H8">
+        <v>104</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>9486.151371</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4.28180071986151</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8.96335860678159</v>
+      </c>
+      <c r="H8" t="n">
         <v>14.8433488405669</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>1.47</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>45533</v>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45576</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="1">
-        <v>2235.4551809999998</v>
-      </c>
-      <c r="D9">
-        <v>1.5</v>
-      </c>
-      <c r="E9">
-        <v>19.561817146153398</v>
-      </c>
-      <c r="F9">
-        <v>6.49</v>
-      </c>
-      <c r="G9">
-        <v>9.83028854045698</v>
-      </c>
-      <c r="H9">
+        <v>125</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>7295.0400390625</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.28180071986151</v>
+      </c>
+      <c r="F9" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="G9" t="n">
+        <v>26.1495614769459</v>
+      </c>
+      <c r="H9" t="n">
         <v>14.7071911538915</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>3.75</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>45534</v>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45575</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="1">
-        <v>100.25</v>
-      </c>
-      <c r="D10">
-        <v>1.46</v>
-      </c>
-      <c r="E10">
-        <v>18.997625578845899</v>
-      </c>
-      <c r="F10">
+        <v>96</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>3793.30534</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.53604607534075</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="G10" t="n">
+        <v>14.4732029620954</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10.4274913828344</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45576</v>
+      </c>
+      <c r="B11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>10012.689476</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.04159569135067</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.9063471169202</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.6415338967120103</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45575</v>
+      </c>
+      <c r="B12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>1.89876339</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.04159569135067</v>
+      </c>
+      <c r="F12" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14.8871688894214</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8.2139158364711307</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45576</v>
+      </c>
+      <c r="B13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>2234.40991210938</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.42657679454032</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="G13" t="n">
+        <v>26.0029239601032</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8.0849810365515502</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45576</v>
+      </c>
+      <c r="B14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>100.480003356934</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.30397754505438</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5.4764293473067</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7.5706487926186803</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45575</v>
+      </c>
+      <c r="B15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>2229.04085</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.44954211884065</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10.4208651049226</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7.0585609779296297</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45576</v>
+      </c>
+      <c r="B16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>101.139999389648</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.478945406733555</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7.33817460630404</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6.6759626640876801</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45573</v>
+      </c>
+      <c r="B17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>5191.96</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-2.13874378586223</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8.68116318208827</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6.5487086851492098</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45576</v>
+      </c>
+      <c r="B18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>18605.817221</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-2.37377521052849</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7.92816473140969</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5.9145235035986001</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45575</v>
+      </c>
+      <c r="B19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>1.36099214</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-3.19231640669571</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10.0814251364338</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.53147769825524</v>
+      </c>
+      <c r="I19" t="n">
         <v>3.18</v>
       </c>
-      <c r="G10">
-        <v>7.4549726586127001</v>
-      </c>
-      <c r="H10">
-        <v>10.4274913828344</v>
-      </c>
-      <c r="I10">
-        <v>2.62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>45531</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="1">
-        <v>5162.78</v>
-      </c>
-      <c r="D11">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="E11">
-        <v>14.2996054499739</v>
-      </c>
-      <c r="F11">
-        <v>2.85</v>
-      </c>
-      <c r="G11">
-        <v>6.7899191646738402</v>
-      </c>
-      <c r="H11">
-        <v>9.6415338967120103</v>
-      </c>
-      <c r="I11">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>45533</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1.87373203</v>
-      </c>
-      <c r="D12">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="E12">
-        <v>14.2996054499739</v>
-      </c>
-      <c r="F12">
-        <v>9.91</v>
-      </c>
-      <c r="G12">
-        <v>15.469788262643799</v>
-      </c>
-      <c r="H12">
-        <v>8.2139158364711307</v>
-      </c>
-      <c r="I12">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>45533</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="1">
-        <v>3742.6224510000002</v>
-      </c>
-      <c r="D13">
-        <v>1.08</v>
-      </c>
-      <c r="E13">
-        <v>13.7582228911072</v>
-      </c>
-      <c r="F13">
-        <v>9.4600000000000009</v>
-      </c>
-      <c r="G13">
-        <v>15.034867532011001</v>
-      </c>
-      <c r="H13">
-        <v>8.0849810365515502</v>
-      </c>
-      <c r="I13">
-        <v>-7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>45534</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="1">
-        <v>3308.6744723195602</v>
-      </c>
-      <c r="D14">
-        <v>0.87</v>
-      </c>
-      <c r="E14">
-        <v>10.954328638178</v>
-      </c>
-      <c r="F14">
-        <v>7.1</v>
-      </c>
-      <c r="G14">
-        <v>11.3188655493522</v>
-      </c>
-      <c r="H14">
-        <v>7.5706487926186803</v>
-      </c>
-      <c r="I14">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>45534</v>
-      </c>
-      <c r="B15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="1">
-        <v>3393.55</v>
-      </c>
-      <c r="D15">
-        <v>0.86</v>
-      </c>
-      <c r="E15">
-        <v>10.8224037644802</v>
-      </c>
-      <c r="F15">
-        <v>2.48</v>
-      </c>
-      <c r="G15">
-        <v>6.2999032085276196</v>
-      </c>
-      <c r="H15">
-        <v>7.0585609779296297</v>
-      </c>
-      <c r="I15">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>45534</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="1">
-        <v>108.870002746582</v>
-      </c>
-      <c r="D16">
-        <v>0.8</v>
-      </c>
-      <c r="E16">
-        <v>10.0338693716146</v>
-      </c>
-      <c r="F16">
-        <v>3.3</v>
-      </c>
-      <c r="G16">
-        <v>6.1206716018768104</v>
-      </c>
-      <c r="H16">
-        <v>6.6759626640876801</v>
-      </c>
-      <c r="I16">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>45534</v>
-      </c>
-      <c r="B17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="1">
-        <v>18579.102225999999</v>
-      </c>
-      <c r="D17">
-        <v>0.66</v>
-      </c>
-      <c r="E17">
-        <v>8.2139158364711307</v>
-      </c>
-      <c r="F17">
-        <v>3.54</v>
-      </c>
-      <c r="G17">
-        <v>8.0437269984020308</v>
-      </c>
-      <c r="H17">
-        <v>6.5487086851492098</v>
-      </c>
-      <c r="I17">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>45534</v>
-      </c>
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="1">
-        <v>17713.619140625</v>
-      </c>
-      <c r="D18">
-        <v>0.65</v>
-      </c>
-      <c r="E18">
-        <v>8.0849810365515502</v>
-      </c>
-      <c r="F18">
-        <v>18</v>
-      </c>
-      <c r="G18">
-        <v>26.3515799532356</v>
-      </c>
-      <c r="H18">
-        <v>5.9145235035986001</v>
-      </c>
-      <c r="I18">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>45534</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" s="1">
-        <v>100.370002746582</v>
-      </c>
-      <c r="D19">
-        <v>0.62</v>
-      </c>
-      <c r="E19">
-        <v>7.6990210897167204</v>
-      </c>
-      <c r="F19">
-        <v>3.82</v>
-      </c>
-      <c r="G19">
-        <v>6.3450304783017897</v>
-      </c>
-      <c r="H19">
-        <v>4.53147769825524</v>
-      </c>
-      <c r="I19">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>45534</v>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45575</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="1">
-        <v>9414.8941670000004</v>
-      </c>
-      <c r="D20">
-        <v>0.59</v>
-      </c>
-      <c r="E20">
-        <v>7.3143248890742898</v>
-      </c>
-      <c r="F20">
-        <v>4.88</v>
-      </c>
-      <c r="G20">
-        <v>7.8011067183189304</v>
-      </c>
-      <c r="H20">
+        <v>93</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>1708.84</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-6.29096647925097</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="G20" t="n">
+        <v>16.7711031084932</v>
+      </c>
+      <c r="H20" t="n">
         <v>3.1650049434697798</v>
       </c>
-      <c r="I20">
+      <c r="I20" t="n">
         <v>3.2</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>45534</v>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45576</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" s="1">
-        <v>10055.168258</v>
-      </c>
-      <c r="D21">
-        <v>0.52</v>
-      </c>
-      <c r="E21">
-        <v>6.4215938714558902</v>
-      </c>
-      <c r="F21">
-        <v>1.49</v>
-      </c>
-      <c r="G21">
-        <v>4.4492816525188497</v>
-      </c>
-      <c r="H21">
+        <v>94</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>109.480003356934</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-9.07875046981781</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8.64016231941116</v>
+      </c>
+      <c r="H21" t="n">
         <v>0.96423528430107397</v>
       </c>
-      <c r="I21">
+      <c r="I21" t="n">
         <v>0.18</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <v>45534</v>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45575</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="1">
-        <v>100.73999786377</v>
-      </c>
-      <c r="D22">
-        <v>0.47</v>
-      </c>
-      <c r="E22">
-        <v>5.7881024430621197</v>
-      </c>
-      <c r="F22">
-        <v>3.59</v>
-      </c>
-      <c r="G22">
-        <v>5.48608289499923</v>
-      </c>
-      <c r="H22">
+        <v>91</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>3383.2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-13.8013140657305</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="G22" t="n">
+        <v>15.0032462786769</v>
+      </c>
+      <c r="H22" t="n">
         <v>0.120066022004939</v>
       </c>
-      <c r="I22">
+      <c r="I22" t="n">
         <v>0.9</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <v>45537</v>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45576</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" s="1">
-        <v>101.709999084473</v>
-      </c>
-      <c r="D23">
-        <v>0.01</v>
-      </c>
-      <c r="E23">
-        <v>0.120066022004939</v>
-      </c>
-      <c r="F23">
-        <v>0.38</v>
-      </c>
-      <c r="G23">
-        <v>-1.8432769846383501</v>
-      </c>
-      <c r="H23">
+        <v>110</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>129992.29</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-15.3591573561266</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="G23" t="n">
+        <v>11.056358977312</v>
+      </c>
+      <c r="H23" t="n">
         <v>-8.1950436713639405</v>
       </c>
-      <c r="I23">
+      <c r="I23" t="n">
         <v>-4.53</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>45534</v>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45576</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" s="1">
-        <v>5.6562000000000001</v>
-      </c>
-      <c r="D24">
-        <v>-0.1</v>
-      </c>
-      <c r="E24">
-        <v>-1.1934219505791099</v>
-      </c>
-      <c r="F24">
-        <v>16.829999999999998</v>
-      </c>
-      <c r="G24">
-        <v>16.129429639058898</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <v>45534</v>
+        <v>95</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-16.0772815163011</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="G24" t="n">
+        <v>9.69047178883859</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45576</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" s="1">
-        <v>2217.6298828125</v>
-      </c>
-      <c r="D25">
-        <v>-1.63</v>
-      </c>
-      <c r="E25">
-        <v>-17.898317592139101</v>
-      </c>
-      <c r="F25">
-        <v>9.4</v>
-      </c>
-      <c r="G25">
-        <v>16.520506319761001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>1990.42</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-21.7202875901512</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-15.41</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-3.86023551687156</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45576</v>
+      </c>
       <c r="B26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3216.81</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-27.9964211209274</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.03776340627613</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="B27" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="1">
-        <v>5.5</v>
+      <c r="C27" s="1" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1377,16 +1516,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" customWidth="1"/>
-    <col min="2" max="2" width="117" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="117" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -1397,7 +1536,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1408,7 +1547,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1419,7 +1558,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1430,7 +1569,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -1441,7 +1580,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1452,7 +1591,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -1463,7 +1602,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1474,7 +1613,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1485,7 +1624,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1496,7 +1635,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1507,7 +1646,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1518,7 +1657,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1529,7 +1668,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1540,7 +1679,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1551,7 +1690,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -1562,7 +1701,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1573,7 +1712,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -1584,7 +1723,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -1595,7 +1734,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1606,7 +1745,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -1617,7 +1756,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>42</v>
       </c>
